--- a/Excel/InfiniteConfig.xlsx
+++ b/Excel/InfiniteConfig.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="2" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="254">
   <si>
     <t>ID</t>
   </si>
@@ -44,19 +44,40 @@
     <t>Attr</t>
   </si>
   <si>
-    <t>RiseAttr</t>
+    <t>AttrRise</t>
   </si>
   <si>
     <t>Def</t>
   </si>
   <si>
-    <t>RiseDef</t>
+    <t>DefRise</t>
   </si>
   <si>
     <t>HP</t>
   </si>
   <si>
-    <t>RiseHp</t>
+    <t>HpRise</t>
+  </si>
+  <si>
+    <t>DamageMul</t>
+  </si>
+  <si>
+    <t>MulRise</t>
+  </si>
+  <si>
+    <t>Strong</t>
+  </si>
+  <si>
+    <t>StrongRise</t>
+  </si>
+  <si>
+    <t>Parry</t>
+  </si>
+  <si>
+    <t>ParrayRise</t>
+  </si>
+  <si>
+    <t>Speed</t>
   </si>
   <si>
     <t>DamageIncrea</t>
@@ -74,9 +95,15 @@
     <t>Accuracy</t>
   </si>
   <si>
+    <t>Miss</t>
+  </si>
+  <si>
     <t>MulDamageResist</t>
   </si>
   <si>
+    <t>Protect</t>
+  </si>
+  <si>
     <t>Exp</t>
   </si>
   <si>
@@ -128,7 +155,7 @@
     <t>800000000000000000000</t>
   </si>
   <si>
-    <t>10000000000000000</t>
+    <t>1000000000000000</t>
   </si>
   <si>
     <t>16000000000000000</t>
@@ -137,10 +164,7 @@
     <t>160000000000000000000000</t>
   </si>
   <si>
-    <t>#</t>
-  </si>
-  <si>
-    <t>1000000000000000000</t>
+    <t>100000000000000000</t>
   </si>
   <si>
     <t>3200000000000000000</t>
@@ -149,7 +173,7 @@
     <t>32000000000000000000000000</t>
   </si>
   <si>
-    <t>100000000000000000000</t>
+    <t>20000000000000000000</t>
   </si>
   <si>
     <t>640000000000000000000</t>
@@ -158,7 +182,7 @@
     <t>6400000000000000000000000000</t>
   </si>
   <si>
-    <t>10000000000000000000000</t>
+    <t>4000000000000000000000</t>
   </si>
   <si>
     <t>128000000000000000000000</t>
@@ -167,7 +191,7 @@
     <t>1280000000000000000000000000000</t>
   </si>
   <si>
-    <t>1000000000000000000000000</t>
+    <t>800000000000000000000000</t>
   </si>
   <si>
     <t>25600000000000000000000000</t>
@@ -176,13 +200,598 @@
     <t>256000000000000000000000000000000</t>
   </si>
   <si>
-    <t>100000000000000000000000000</t>
+    <t>80000000000000000000000000</t>
   </si>
   <si>
     <t>5120000000000000000000000000</t>
   </si>
   <si>
-    <t>51200000000000000000000000000000000</t>
+    <t>512000000000000000000000000000000000</t>
+  </si>
+  <si>
+    <t>8000000000000000000000000000</t>
+  </si>
+  <si>
+    <t>512000000000000000000000000000</t>
+  </si>
+  <si>
+    <t>999000000000000000000000000000000000000</t>
+  </si>
+  <si>
+    <t>160000000000000000000000000000</t>
+  </si>
+  <si>
+    <t>5120000000000000000000000000000</t>
+  </si>
+  <si>
+    <t>999000000000000000000000000000000000000000</t>
+  </si>
+  <si>
+    <t>3200000000000000000000000000000</t>
+  </si>
+  <si>
+    <t>51200000000000000000000000000000</t>
+  </si>
+  <si>
+    <t>999000000000000000000000000000000000000000000</t>
+  </si>
+  <si>
+    <t>64000000000000000000000000000000</t>
+  </si>
+  <si>
+    <t>512000000000000000000000000000000</t>
+  </si>
+  <si>
+    <t>999000000000000000000000000000000000000000000000</t>
+  </si>
+  <si>
+    <t>1200000000000000000000000000000000</t>
+  </si>
+  <si>
+    <t>5120000000000000000000000000000000</t>
+  </si>
+  <si>
+    <t>999000000000000000000000000000000000000000000000000</t>
+  </si>
+  <si>
+    <t>900涧</t>
+  </si>
+  <si>
+    <t>9000涧</t>
+  </si>
+  <si>
+    <t>99恒</t>
+  </si>
+  <si>
+    <t>90正</t>
+  </si>
+  <si>
+    <t>99900恒</t>
+  </si>
+  <si>
+    <t>9正</t>
+  </si>
+  <si>
+    <t>9000正</t>
+  </si>
+  <si>
+    <t>9990河</t>
+  </si>
+  <si>
+    <t>4万</t>
+  </si>
+  <si>
+    <t>90载</t>
+  </si>
+  <si>
+    <t>999沙</t>
+  </si>
+  <si>
+    <t>80万</t>
+  </si>
+  <si>
+    <t>900正</t>
+  </si>
+  <si>
+    <t>9000载</t>
+  </si>
+  <si>
+    <t>99阿</t>
+  </si>
+  <si>
+    <t>1600万</t>
+  </si>
+  <si>
+    <t>90极</t>
+  </si>
+  <si>
+    <t>9990阿</t>
+  </si>
+  <si>
+    <t>3亿</t>
+  </si>
+  <si>
+    <t>9载</t>
+  </si>
+  <si>
+    <t>9000极</t>
+  </si>
+  <si>
+    <t>99僧</t>
+  </si>
+  <si>
+    <t>60亿</t>
+  </si>
+  <si>
+    <t>90恒</t>
+  </si>
+  <si>
+    <t>9990僧</t>
+  </si>
+  <si>
+    <t>1200亿</t>
+  </si>
+  <si>
+    <t>900载</t>
+  </si>
+  <si>
+    <t>9000恒</t>
+  </si>
+  <si>
+    <t>999祇</t>
+  </si>
+  <si>
+    <t>2兆</t>
+  </si>
+  <si>
+    <t>90河</t>
+  </si>
+  <si>
+    <t>99那</t>
+  </si>
+  <si>
+    <t>40兆</t>
+  </si>
+  <si>
+    <t>10极</t>
+  </si>
+  <si>
+    <t>9000河</t>
+  </si>
+  <si>
+    <t>99900那</t>
+  </si>
+  <si>
+    <t>800兆</t>
+  </si>
+  <si>
+    <t>100极</t>
+  </si>
+  <si>
+    <t>90沙</t>
+  </si>
+  <si>
+    <t>9990由</t>
+  </si>
+  <si>
+    <t>16000兆</t>
+  </si>
+  <si>
+    <t>1000极</t>
+  </si>
+  <si>
+    <t>9000沙</t>
+  </si>
+  <si>
+    <t>999他</t>
+  </si>
+  <si>
+    <t>32京</t>
+  </si>
+  <si>
+    <t>10000极</t>
+  </si>
+  <si>
+    <t>90阿</t>
+  </si>
+  <si>
+    <t>999不</t>
+  </si>
+  <si>
+    <t>640京</t>
+  </si>
+  <si>
+    <t>1恒</t>
+  </si>
+  <si>
+    <t>9000阿</t>
+  </si>
+  <si>
+    <t>99可</t>
+  </si>
+  <si>
+    <t>12800京</t>
+  </si>
+  <si>
+    <t>10恒</t>
+  </si>
+  <si>
+    <t>9999阿</t>
+  </si>
+  <si>
+    <t>99000可</t>
+  </si>
+  <si>
+    <t>900垓</t>
+  </si>
+  <si>
+    <t>100恒</t>
+  </si>
+  <si>
+    <t>9999僧</t>
+  </si>
+  <si>
+    <t>9900思</t>
+  </si>
+  <si>
+    <t>90秭</t>
+  </si>
+  <si>
+    <t>1000恒</t>
+  </si>
+  <si>
+    <t>9999祇</t>
+  </si>
+  <si>
+    <t>990议</t>
+  </si>
+  <si>
+    <t>9穰</t>
+  </si>
+  <si>
+    <t>1河</t>
+  </si>
+  <si>
+    <t>9999那</t>
+  </si>
+  <si>
+    <t>99无</t>
+  </si>
+  <si>
+    <t>9990穰</t>
+  </si>
+  <si>
+    <t>10河</t>
+  </si>
+  <si>
+    <t>9999由</t>
+  </si>
+  <si>
+    <t>99000无</t>
+  </si>
+  <si>
+    <t>999沟</t>
+  </si>
+  <si>
+    <t>1000河</t>
+  </si>
+  <si>
+    <t>9999他</t>
+  </si>
+  <si>
+    <t>99000量</t>
+  </si>
+  <si>
+    <t>99涧</t>
+  </si>
+  <si>
+    <t>10亿</t>
+  </si>
+  <si>
+    <t>100沙</t>
+  </si>
+  <si>
+    <t>9999不</t>
+  </si>
+  <si>
+    <t>99000大</t>
+  </si>
+  <si>
+    <t>1000亿</t>
+  </si>
+  <si>
+    <t>10阿</t>
+  </si>
+  <si>
+    <t>9999可</t>
+  </si>
+  <si>
+    <t>99000数</t>
+  </si>
+  <si>
+    <t>9999正</t>
+  </si>
+  <si>
+    <t>10兆</t>
+  </si>
+  <si>
+    <t>1僧</t>
+  </si>
+  <si>
+    <t>9999思</t>
+  </si>
+  <si>
+    <t>99000古</t>
+  </si>
+  <si>
+    <t>999载</t>
+  </si>
+  <si>
+    <t>1000兆</t>
+  </si>
+  <si>
+    <t>1E+71</t>
+  </si>
+  <si>
+    <t>1E+104</t>
+  </si>
+  <si>
+    <t>1E+129</t>
+  </si>
+  <si>
+    <t>1E+50</t>
+  </si>
+  <si>
+    <t>1E+17</t>
+  </si>
+  <si>
+    <t>1E+74</t>
+  </si>
+  <si>
+    <t>1E+108</t>
+  </si>
+  <si>
+    <t>1E+133</t>
+  </si>
+  <si>
+    <t>1E+53</t>
+  </si>
+  <si>
+    <t>1E+19</t>
+  </si>
+  <si>
+    <t>1E+77</t>
+  </si>
+  <si>
+    <t>1E+112</t>
+  </si>
+  <si>
+    <t>1E+137</t>
+  </si>
+  <si>
+    <t>1E+56</t>
+  </si>
+  <si>
+    <t>1E+21</t>
+  </si>
+  <si>
+    <t>1E+81</t>
+  </si>
+  <si>
+    <t>1E+116</t>
+  </si>
+  <si>
+    <t>1E+141</t>
+  </si>
+  <si>
+    <t>1E+59</t>
+  </si>
+  <si>
+    <t>1E+23</t>
+  </si>
+  <si>
+    <t>1E+85</t>
+  </si>
+  <si>
+    <t>1E+120</t>
+  </si>
+  <si>
+    <t>1E+145</t>
+  </si>
+  <si>
+    <t>1E+62</t>
+  </si>
+  <si>
+    <t>1E+25</t>
+  </si>
+  <si>
+    <t>1E+89</t>
+  </si>
+  <si>
+    <t>1E+125</t>
+  </si>
+  <si>
+    <t>1E+149</t>
+  </si>
+  <si>
+    <t>1E+65</t>
+  </si>
+  <si>
+    <t>1E+27</t>
+  </si>
+  <si>
+    <t>1E+95</t>
+  </si>
+  <si>
+    <t>1E+130</t>
+  </si>
+  <si>
+    <t>1E+154</t>
+  </si>
+  <si>
+    <t>1E+70</t>
+  </si>
+  <si>
+    <t>1E+30</t>
+  </si>
+  <si>
+    <t>1E+100</t>
+  </si>
+  <si>
+    <t>1E+135</t>
+  </si>
+  <si>
+    <t>1E+159</t>
+  </si>
+  <si>
+    <t>1E+75</t>
+  </si>
+  <si>
+    <t>1E+33</t>
+  </si>
+  <si>
+    <t>1E+105</t>
+  </si>
+  <si>
+    <t>1E+140</t>
+  </si>
+  <si>
+    <t>1E+164</t>
+  </si>
+  <si>
+    <t>1E+80</t>
+  </si>
+  <si>
+    <t>1E+37</t>
+  </si>
+  <si>
+    <t>1E+110</t>
+  </si>
+  <si>
+    <t>1E+169</t>
+  </si>
+  <si>
+    <t>1E+41</t>
+  </si>
+  <si>
+    <t>1E+4</t>
+  </si>
+  <si>
+    <t>1E+115</t>
+  </si>
+  <si>
+    <t>1E+150</t>
+  </si>
+  <si>
+    <t>1E+174</t>
+  </si>
+  <si>
+    <t>1E+90</t>
+  </si>
+  <si>
+    <t>1E+45</t>
+  </si>
+  <si>
+    <t>1E+5</t>
+  </si>
+  <si>
+    <t>1E+155</t>
+  </si>
+  <si>
+    <t>1E+179</t>
+  </si>
+  <si>
+    <t>1E+49</t>
+  </si>
+  <si>
+    <t>1E+8</t>
+  </si>
+  <si>
+    <t>1E+160</t>
+  </si>
+  <si>
+    <t>1E+184</t>
+  </si>
+  <si>
+    <t>1E+51</t>
+  </si>
+  <si>
+    <t>1E+11</t>
+  </si>
+  <si>
+    <t>1E+165</t>
+  </si>
+  <si>
+    <t>1E+189</t>
+  </si>
+  <si>
+    <t>1E+14</t>
+  </si>
+  <si>
+    <t>1E+170</t>
+  </si>
+  <si>
+    <t>1E+194</t>
+  </si>
+  <si>
+    <t>1E+55</t>
+  </si>
+  <si>
+    <t>1E+175</t>
+  </si>
+  <si>
+    <t>1E+199</t>
+  </si>
+  <si>
+    <t>1E+57</t>
+  </si>
+  <si>
+    <t>1E+20</t>
+  </si>
+  <si>
+    <t>1E+180</t>
+  </si>
+  <si>
+    <t>1E+204</t>
+  </si>
+  <si>
+    <t>1E+209</t>
+  </si>
+  <si>
+    <t>1E+60</t>
+  </si>
+  <si>
+    <t>1E+214</t>
+  </si>
+  <si>
+    <t>1E+61</t>
+  </si>
+  <si>
+    <t>1E+31</t>
+  </si>
+  <si>
+    <t>1E+219</t>
+  </si>
+  <si>
+    <t>1E+35</t>
+  </si>
+  <si>
+    <t>1E+224</t>
+  </si>
+  <si>
+    <t>1E+63</t>
+  </si>
+  <si>
+    <t>1E+39</t>
+  </si>
+  <si>
+    <t>1E+1</t>
+  </si>
+  <si>
+    <t>1E+2</t>
+  </si>
+  <si>
+    <t>1E+3</t>
   </si>
 </sst>
 </file>
@@ -196,7 +805,7 @@
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -211,9 +820,20 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
       <sz val="9"/>
       <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="3" tint="0.6"/>
       <name val="等线"/>
       <charset val="134"/>
     </font>
@@ -362,12 +982,30 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -539,12 +1177,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -686,161 +1318,202 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="176" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="176" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="176" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="176" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
+    <xf numFmtId="176" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1160,338 +1833,498 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S36"/>
+  <dimension ref="A1:AB215"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
-    <col min="2" max="2" width="8" style="2" customWidth="1"/>
-    <col min="3" max="3" width="9.875" style="1" customWidth="1"/>
-    <col min="4" max="5" width="11.125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="19" style="3" customWidth="1"/>
-    <col min="7" max="7" width="19.625" style="3" customWidth="1"/>
-    <col min="8" max="8" width="18.875" style="3" customWidth="1"/>
-    <col min="9" max="9" width="17.125" style="3" customWidth="1"/>
-    <col min="10" max="10" width="28.875" style="3" customWidth="1"/>
-    <col min="11" max="11" width="28.25" style="3" customWidth="1"/>
-    <col min="12" max="12" width="7.125" style="2" customWidth="1"/>
-    <col min="13" max="14" width="6.375" style="2" customWidth="1"/>
-    <col min="15" max="15" width="8" style="2" customWidth="1"/>
-    <col min="16" max="17" width="5.875" style="2" customWidth="1"/>
-    <col min="18" max="18" width="12.875" style="2" customWidth="1"/>
-    <col min="19" max="19" width="13.375" style="2" customWidth="1"/>
-    <col min="20" max="16384" width="9" style="2"/>
+    <col min="1" max="1" width="3" style="5" customWidth="1"/>
+    <col min="2" max="2" width="3.375" style="5" customWidth="1"/>
+    <col min="3" max="3" width="3.125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="7.875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="7.25" style="1" customWidth="1"/>
+    <col min="6" max="6" width="28.5833333333333" style="6" customWidth="1"/>
+    <col min="7" max="7" width="15.25" style="7" customWidth="1"/>
+    <col min="8" max="8" width="34.0833333333333" style="6" customWidth="1"/>
+    <col min="9" max="9" width="9.75" style="7" customWidth="1"/>
+    <col min="10" max="10" width="26.0833333333333" style="6" customWidth="1"/>
+    <col min="11" max="11" width="9.75" style="7" customWidth="1"/>
+    <col min="12" max="12" width="13.6666666666667" style="7" customWidth="1"/>
+    <col min="13" max="14" width="10" style="7" customWidth="1"/>
+    <col min="15" max="15" width="8.83333333333333" style="7" customWidth="1"/>
+    <col min="16" max="18" width="12.125" style="5" customWidth="1"/>
+    <col min="19" max="19" width="12.5833333333333" style="5" customWidth="1"/>
+    <col min="20" max="21" width="6.375" style="5" customWidth="1"/>
+    <col min="22" max="22" width="8" style="5" customWidth="1"/>
+    <col min="23" max="23" width="5.875" style="5" customWidth="1"/>
+    <col min="24" max="25" width="7.375" style="5" customWidth="1"/>
+    <col min="26" max="26" width="10.25" style="5" customWidth="1"/>
+    <col min="27" max="27" width="19.7916666666667" style="5" customWidth="1"/>
+    <col min="28" max="28" width="17.6583333333333" style="5" customWidth="1"/>
+    <col min="29" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:19">
-      <c r="A1" s="2"/>
-      <c r="B1" s="2"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
-      <c r="I1" s="4"/>
-      <c r="J1" s="4"/>
-      <c r="K1" s="4"/>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2"/>
-      <c r="N1" s="2"/>
-      <c r="O1" s="2"/>
-      <c r="P1" s="2"/>
-      <c r="Q1" s="2"/>
-      <c r="R1" s="2"/>
-      <c r="S1" s="2"/>
-    </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:19">
-      <c r="A2" s="2"/>
-      <c r="B2" s="2"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
-      <c r="J2" s="4"/>
-      <c r="K2" s="4"/>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2"/>
-      <c r="N2" s="2"/>
-      <c r="O2" s="2"/>
-      <c r="P2" s="2"/>
-      <c r="Q2" s="2"/>
-      <c r="R2" s="2"/>
-      <c r="S2" s="2"/>
-    </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:19">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2"/>
-      <c r="C3" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="D3" s="5" t="s">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:28">
+      <c r="A1" s="5"/>
+      <c r="B1" s="5"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="8"/>
+      <c r="I1" s="5"/>
+      <c r="J1" s="8"/>
+      <c r="K1" s="5"/>
+      <c r="L1" s="5"/>
+      <c r="M1" s="5"/>
+      <c r="N1" s="5"/>
+      <c r="O1" s="5"/>
+      <c r="P1" s="5"/>
+      <c r="Q1" s="5"/>
+      <c r="R1" s="5"/>
+      <c r="S1" s="5"/>
+      <c r="T1" s="5"/>
+      <c r="U1" s="5"/>
+      <c r="V1" s="5"/>
+      <c r="W1" s="5"/>
+      <c r="X1" s="5"/>
+      <c r="Y1" s="5"/>
+      <c r="Z1" s="5"/>
+      <c r="AA1" s="5"/>
+      <c r="AB1" s="5"/>
+    </row>
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:28">
+      <c r="A2" s="5"/>
+      <c r="B2" s="5"/>
+      <c r="F2" s="8"/>
+      <c r="G2" s="5"/>
+      <c r="H2" s="8"/>
+      <c r="I2" s="5"/>
+      <c r="J2" s="8"/>
+      <c r="K2" s="5"/>
+      <c r="L2" s="5"/>
+      <c r="M2" s="5"/>
+      <c r="N2" s="5"/>
+      <c r="O2" s="5"/>
+      <c r="P2" s="5"/>
+      <c r="Q2" s="5"/>
+      <c r="R2" s="5"/>
+      <c r="S2" s="5"/>
+      <c r="T2" s="5"/>
+      <c r="U2" s="5"/>
+      <c r="V2" s="5"/>
+      <c r="W2" s="5"/>
+      <c r="X2" s="5"/>
+      <c r="Y2" s="5"/>
+      <c r="Z2" s="5"/>
+      <c r="AA2" s="5"/>
+      <c r="AB2" s="5"/>
+    </row>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:28">
+      <c r="A3" s="5"/>
+      <c r="B3" s="5"/>
+      <c r="C3" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F3" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="G3" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="H3" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="I3" s="6" t="s">
+      <c r="I3" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="6" t="s">
+      <c r="J3" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="K3" s="6" t="s">
+      <c r="K3" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="L3" s="5" t="s">
+      <c r="L3" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="M3" s="5" t="s">
+      <c r="M3" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="N3" s="5" t="s">
+      <c r="N3" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="O3" s="5" t="s">
+      <c r="O3" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="P3" s="5" t="s">
+      <c r="P3" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="Q3" s="5" t="s">
+      <c r="Q3" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="R3" s="10" t="s">
+      <c r="R3" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="S3" s="10" t="s">
+      <c r="S3" s="9" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:19">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="5" t="s">
+      <c r="T3" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="U3" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="V3" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="W3" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="X3" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y3" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z3" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="AA3" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="AB3" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:28">
+      <c r="A4" s="5"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="F4" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="G4" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="H4" s="6" t="s">
+      <c r="H4" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="I4" s="6" t="s">
+      <c r="I4" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="6" t="s">
+      <c r="J4" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="K4" s="6" t="s">
+      <c r="K4" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="L4" s="5" t="s">
+      <c r="L4" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="M4" s="5" t="s">
+      <c r="M4" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="N4" s="5" t="s">
+      <c r="N4" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="O4" s="5" t="s">
+      <c r="O4" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="P4" s="5" t="s">
+      <c r="P4" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="Q4" s="5" t="s">
+      <c r="Q4" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="R4" s="10" t="s">
+      <c r="R4" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="S4" s="10" t="s">
+      <c r="S4" s="9" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:19">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="5" t="s">
+      <c r="T4" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="U4" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="D5" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="F5" s="6" t="s">
+      <c r="V4" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="G5" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="H5" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="I5" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="J5" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="K5" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="L5" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="M5" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="N5" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="O5" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="P5" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q5" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="R5" s="10" t="s">
+      <c r="W4" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="S5" s="10" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="6" customHeight="1" spans="3:19">
+      <c r="X4" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y4" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z4" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="AA4" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="AB4" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:28">
+      <c r="A5" s="5"/>
+      <c r="B5" s="5"/>
+      <c r="C5" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="G5" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="H5" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="I5" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="J5" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="K5" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="L5" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="M5" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="N5" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="O5" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="P5" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q5" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="R5" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="S5" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="T5" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="U5" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="V5" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="W5" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="X5" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y5" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="Z5" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="AA5" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="AB5" s="11" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" customHeight="1" spans="1:28">
       <c r="C6" s="1">
         <v>1</v>
       </c>
-      <c r="D6" s="7">
+      <c r="D6" s="12">
         <v>1</v>
       </c>
-      <c r="E6" s="7">
-        <v>100</v>
-      </c>
-      <c r="F6" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="G6" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="H6" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="I6" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="J6" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="K6" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="L6" s="9">
-        <v>100</v>
-      </c>
-      <c r="M6" s="9">
-        <v>100</v>
-      </c>
-      <c r="N6" s="9">
-        <v>100</v>
-      </c>
-      <c r="O6" s="9">
-        <v>100</v>
-      </c>
-      <c r="P6" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="9">
-        <v>99</v>
-      </c>
-      <c r="R6" s="8">
+      <c r="E6" s="12">
+        <v>100</v>
+      </c>
+      <c r="F6" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="G6" s="14">
+        <v>1</v>
+      </c>
+      <c r="H6" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I6" s="14">
+        <v>1</v>
+      </c>
+      <c r="J6" s="26" t="s">
+        <v>31</v>
+      </c>
+      <c r="K6" s="14">
+        <v>1</v>
+      </c>
+      <c r="L6" s="14">
+        <v>0</v>
+      </c>
+      <c r="M6" s="14">
+        <v>0</v>
+      </c>
+      <c r="N6" s="14">
+        <v>0</v>
+      </c>
+      <c r="O6" s="14">
+        <v>0</v>
+      </c>
+      <c r="P6" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="1">
+        <v>0</v>
+      </c>
+      <c r="R6" s="1">
+        <v>0</v>
+      </c>
+      <c r="S6" s="15">
+        <v>100</v>
+      </c>
+      <c r="T6" s="15">
+        <v>100</v>
+      </c>
+      <c r="U6" s="15">
+        <v>100</v>
+      </c>
+      <c r="V6" s="15">
+        <v>100</v>
+      </c>
+      <c r="W6" s="15">
+        <v>0</v>
+      </c>
+      <c r="X6" s="15">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="15">
+        <v>70</v>
+      </c>
+      <c r="Z6" s="15">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="13">
         <v>10000000000</v>
       </c>
-      <c r="S6" s="8">
+      <c r="AB6" s="13">
         <v>10000000000</v>
       </c>
     </row>
-    <row r="7" customHeight="1" spans="3:19">
+    <row r="7" customHeight="1" spans="1:28">
       <c r="C7" s="1">
         <v>2</v>
       </c>
       <c r="D7" s="1">
-        <f t="shared" ref="D7:D22" si="0">E6+1</f>
+        <f t="shared" ref="D7:D65" si="0">E6+1</f>
         <v>101</v>
       </c>
       <c r="E7" s="1">
-        <f t="shared" ref="E7:E22" si="1">E6+100</f>
+        <f t="shared" ref="E7:E65" si="1">E6+100</f>
         <v>200</v>
       </c>
-      <c r="F7" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="G7" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="H7" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="I7" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="J7" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="K7" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="L7" s="9">
+      <c r="F7" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="G7" s="14">
+        <v>1</v>
+      </c>
+      <c r="H7" s="26" t="s">
+        <v>33</v>
+      </c>
+      <c r="I7" s="14">
+        <v>1</v>
+      </c>
+      <c r="J7" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="K7" s="14">
+        <v>1</v>
+      </c>
+      <c r="L7" s="14">
+        <v>0</v>
+      </c>
+      <c r="M7" s="14">
+        <v>0</v>
+      </c>
+      <c r="N7" s="14">
+        <v>0</v>
+      </c>
+      <c r="O7" s="14">
+        <v>0</v>
+      </c>
+      <c r="P7" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="1">
+        <v>0</v>
+      </c>
+      <c r="R7" s="1">
+        <v>0</v>
+      </c>
+      <c r="S7" s="15">
         <v>200</v>
       </c>
-      <c r="M7" s="9">
+      <c r="T7" s="15">
         <v>200</v>
       </c>
-      <c r="N7" s="9">
+      <c r="U7" s="15">
         <v>200</v>
       </c>
-      <c r="O7" s="9">
+      <c r="V7" s="15">
         <v>200</v>
       </c>
-      <c r="P7" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="9">
-        <v>99</v>
-      </c>
-      <c r="R7" s="8">
+      <c r="W7" s="15">
+        <v>0</v>
+      </c>
+      <c r="X7" s="15">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="15">
+        <v>70</v>
+      </c>
+      <c r="Z7" s="15">
+        <v>0</v>
+      </c>
+      <c r="AA7" s="13">
         <v>500000000000</v>
       </c>
-      <c r="S7" s="8">
+      <c r="AB7" s="13">
         <v>500000000000</v>
       </c>
     </row>
-    <row r="8" customHeight="1" spans="3:19">
+    <row r="8" customHeight="1" spans="1:28">
       <c r="C8" s="1">
         <v>3</v>
       </c>
@@ -1503,50 +2336,77 @@
         <f t="shared" si="1"/>
         <v>300</v>
       </c>
-      <c r="F8" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="G8" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="H8" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="I8" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="J8" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="K8" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="L8" s="9">
+      <c r="F8" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="G8" s="14">
+        <v>1</v>
+      </c>
+      <c r="H8" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="I8" s="14">
+        <v>1</v>
+      </c>
+      <c r="J8" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="K8" s="14">
+        <v>1</v>
+      </c>
+      <c r="L8" s="14">
+        <v>0</v>
+      </c>
+      <c r="M8" s="14">
+        <v>0</v>
+      </c>
+      <c r="N8" s="14">
+        <v>0</v>
+      </c>
+      <c r="O8" s="14">
+        <v>0</v>
+      </c>
+      <c r="P8" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="1">
+        <v>0</v>
+      </c>
+      <c r="R8" s="1">
+        <v>0</v>
+      </c>
+      <c r="S8" s="15">
         <v>300</v>
       </c>
-      <c r="M8" s="9">
+      <c r="T8" s="15">
         <v>300</v>
       </c>
-      <c r="N8" s="9">
+      <c r="U8" s="15">
         <v>300</v>
       </c>
-      <c r="O8" s="9">
+      <c r="V8" s="15">
         <v>300</v>
       </c>
-      <c r="P8" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="9">
-        <v>99</v>
-      </c>
-      <c r="R8" s="8">
+      <c r="W8" s="15">
+        <v>0</v>
+      </c>
+      <c r="X8" s="15">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="15">
+        <v>70</v>
+      </c>
+      <c r="Z8" s="15">
+        <v>0</v>
+      </c>
+      <c r="AA8" s="13">
         <v>1000000000000</v>
       </c>
-      <c r="S8" s="8">
+      <c r="AB8" s="13">
         <v>1000000000000</v>
       </c>
     </row>
-    <row r="9" customHeight="1" spans="3:19">
+    <row r="9" customHeight="1" spans="1:28">
       <c r="C9" s="1">
         <v>4</v>
       </c>
@@ -1558,50 +2418,77 @@
         <f t="shared" si="1"/>
         <v>400</v>
       </c>
-      <c r="F9" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="G9" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="H9" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="I9" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="J9" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="K9" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="L9" s="9">
+      <c r="F9" s="26" t="s">
+        <v>38</v>
+      </c>
+      <c r="G9" s="14">
+        <v>1</v>
+      </c>
+      <c r="H9" s="26" t="s">
+        <v>39</v>
+      </c>
+      <c r="I9" s="14">
+        <v>1</v>
+      </c>
+      <c r="J9" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="K9" s="14">
+        <v>1</v>
+      </c>
+      <c r="L9" s="14">
+        <v>0</v>
+      </c>
+      <c r="M9" s="14">
+        <v>0</v>
+      </c>
+      <c r="N9" s="14">
+        <v>0</v>
+      </c>
+      <c r="O9" s="14">
+        <v>0</v>
+      </c>
+      <c r="P9" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="1">
+        <v>0</v>
+      </c>
+      <c r="R9" s="1">
+        <v>0</v>
+      </c>
+      <c r="S9" s="15">
         <v>400</v>
       </c>
-      <c r="M9" s="9">
+      <c r="T9" s="15">
         <v>400</v>
       </c>
-      <c r="N9" s="9">
+      <c r="U9" s="15">
         <v>400</v>
       </c>
-      <c r="O9" s="9">
+      <c r="V9" s="15">
         <v>400</v>
       </c>
-      <c r="P9" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="9">
-        <v>99</v>
-      </c>
-      <c r="R9" s="8">
+      <c r="W9" s="15">
+        <v>0</v>
+      </c>
+      <c r="X9" s="15">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="15">
+        <v>70</v>
+      </c>
+      <c r="Z9" s="15">
+        <v>0</v>
+      </c>
+      <c r="AA9" s="13">
         <v>5000000000000</v>
       </c>
-      <c r="S9" s="8">
+      <c r="AB9" s="13">
         <v>5000000000000</v>
       </c>
     </row>
-    <row r="10" customHeight="1" spans="3:19">
+    <row r="10" customHeight="1" spans="1:28">
       <c r="C10" s="1">
         <v>5</v>
       </c>
@@ -1613,56 +2500,77 @@
         <f t="shared" si="1"/>
         <v>500</v>
       </c>
-      <c r="F10" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="G10" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="H10" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="I10" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="J10" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="K10" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="L10" s="9">
+      <c r="F10" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="G10" s="14">
+        <v>1</v>
+      </c>
+      <c r="H10" s="26" t="s">
+        <v>42</v>
+      </c>
+      <c r="I10" s="14">
+        <v>1</v>
+      </c>
+      <c r="J10" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="K10" s="14">
+        <v>1</v>
+      </c>
+      <c r="L10" s="14">
+        <v>0</v>
+      </c>
+      <c r="M10" s="14">
+        <v>0</v>
+      </c>
+      <c r="N10" s="14">
+        <v>0</v>
+      </c>
+      <c r="O10" s="14">
+        <v>0</v>
+      </c>
+      <c r="P10" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="1">
+        <v>0</v>
+      </c>
+      <c r="R10" s="1">
+        <v>0</v>
+      </c>
+      <c r="S10" s="15">
         <v>500</v>
       </c>
-      <c r="M10" s="9">
+      <c r="T10" s="15">
         <v>500</v>
       </c>
-      <c r="N10" s="9">
+      <c r="U10" s="15">
         <v>500</v>
       </c>
-      <c r="O10" s="9">
+      <c r="V10" s="15">
         <v>500</v>
       </c>
-      <c r="P10" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="9">
-        <v>99</v>
-      </c>
-      <c r="R10" s="8">
+      <c r="W10" s="15">
+        <v>0</v>
+      </c>
+      <c r="X10" s="15">
+        <v>0</v>
+      </c>
+      <c r="Y10" s="15">
+        <v>70</v>
+      </c>
+      <c r="Z10" s="15">
+        <v>0</v>
+      </c>
+      <c r="AA10" s="13">
         <v>10000000000000</v>
       </c>
-      <c r="S10" s="8">
+      <c r="AB10" s="13">
         <v>10000000000000</v>
       </c>
     </row>
-    <row r="11" customHeight="1" spans="1:19">
-      <c r="A11" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>35</v>
-      </c>
+    <row r="11" customHeight="1" spans="1:28">
       <c r="C11" s="1">
         <v>6</v>
       </c>
@@ -1674,56 +2582,77 @@
         <f t="shared" si="1"/>
         <v>600</v>
       </c>
-      <c r="F11" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="G11" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="H11" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="I11" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="J11" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="K11" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="L11" s="9">
+      <c r="F11" s="26" t="s">
+        <v>44</v>
+      </c>
+      <c r="G11" s="14">
+        <v>1</v>
+      </c>
+      <c r="H11" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="I11" s="14">
+        <v>1</v>
+      </c>
+      <c r="J11" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="K11" s="14">
+        <v>1</v>
+      </c>
+      <c r="L11" s="14">
+        <v>0</v>
+      </c>
+      <c r="M11" s="14">
+        <v>0</v>
+      </c>
+      <c r="N11" s="14">
+        <v>0</v>
+      </c>
+      <c r="O11" s="14">
+        <v>0</v>
+      </c>
+      <c r="P11" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="1">
+        <v>0</v>
+      </c>
+      <c r="R11" s="1">
+        <v>0</v>
+      </c>
+      <c r="S11" s="15">
         <v>600</v>
       </c>
-      <c r="M11" s="9">
+      <c r="T11" s="15">
         <v>600</v>
       </c>
-      <c r="N11" s="9">
+      <c r="U11" s="15">
         <v>600</v>
       </c>
-      <c r="O11" s="9">
+      <c r="V11" s="15">
         <v>600</v>
       </c>
-      <c r="P11" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="9">
-        <v>99</v>
-      </c>
-      <c r="R11" s="8">
-        <v>1000000000000</v>
-      </c>
-      <c r="S11" s="8">
-        <v>1000000000000</v>
-      </c>
-    </row>
-    <row r="12" customHeight="1" spans="1:19">
-      <c r="A12" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>35</v>
-      </c>
+      <c r="W11" s="15">
+        <v>10</v>
+      </c>
+      <c r="X11" s="15">
+        <v>0</v>
+      </c>
+      <c r="Y11" s="15">
+        <v>70</v>
+      </c>
+      <c r="Z11" s="15">
+        <v>0</v>
+      </c>
+      <c r="AA11" s="13">
+        <v>100000000000000</v>
+      </c>
+      <c r="AB11" s="13">
+        <v>100000000000000</v>
+      </c>
+    </row>
+    <row r="12" customHeight="1" spans="1:28">
       <c r="C12" s="1">
         <v>7</v>
       </c>
@@ -1735,56 +2664,77 @@
         <f t="shared" si="1"/>
         <v>700</v>
       </c>
-      <c r="F12" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="G12" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="H12" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="I12" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="J12" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="K12" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="L12" s="9">
+      <c r="F12" s="26" t="s">
+        <v>47</v>
+      </c>
+      <c r="G12" s="14">
+        <v>1</v>
+      </c>
+      <c r="H12" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="I12" s="14">
+        <v>1</v>
+      </c>
+      <c r="J12" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="K12" s="14">
+        <v>1</v>
+      </c>
+      <c r="L12" s="14">
+        <v>0</v>
+      </c>
+      <c r="M12" s="14">
+        <v>0</v>
+      </c>
+      <c r="N12" s="14">
+        <v>0</v>
+      </c>
+      <c r="O12" s="14">
+        <v>0</v>
+      </c>
+      <c r="P12" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="1">
+        <v>0</v>
+      </c>
+      <c r="R12" s="1">
+        <v>0</v>
+      </c>
+      <c r="S12" s="15">
         <v>700</v>
       </c>
-      <c r="M12" s="9">
+      <c r="T12" s="15">
         <v>700</v>
       </c>
-      <c r="N12" s="9">
+      <c r="U12" s="15">
         <v>700</v>
       </c>
-      <c r="O12" s="9">
+      <c r="V12" s="15">
         <v>700</v>
       </c>
-      <c r="P12" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="9">
-        <v>99</v>
-      </c>
-      <c r="R12" s="8">
-        <v>1000000000000</v>
-      </c>
-      <c r="S12" s="8">
-        <v>1000000000000</v>
-      </c>
-    </row>
-    <row r="13" customHeight="1" spans="1:19">
-      <c r="A13" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>35</v>
-      </c>
+      <c r="W12" s="15">
+        <v>20</v>
+      </c>
+      <c r="X12" s="15">
+        <v>0</v>
+      </c>
+      <c r="Y12" s="15">
+        <v>70</v>
+      </c>
+      <c r="Z12" s="15">
+        <v>30</v>
+      </c>
+      <c r="AA12" s="13">
+        <v>200000000000000</v>
+      </c>
+      <c r="AB12" s="13">
+        <v>200000000000000</v>
+      </c>
+    </row>
+    <row r="13" customHeight="1" spans="1:28">
       <c r="C13" s="1">
         <v>8</v>
       </c>
@@ -1796,56 +2746,77 @@
         <f t="shared" si="1"/>
         <v>800</v>
       </c>
-      <c r="F13" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="G13" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="H13" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="I13" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="J13" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="K13" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="L13" s="9">
+      <c r="F13" s="26" t="s">
+        <v>50</v>
+      </c>
+      <c r="G13" s="14">
+        <v>1</v>
+      </c>
+      <c r="H13" s="26" t="s">
+        <v>51</v>
+      </c>
+      <c r="I13" s="14">
+        <v>1</v>
+      </c>
+      <c r="J13" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="K13" s="14">
+        <v>1</v>
+      </c>
+      <c r="L13" s="14">
+        <v>0</v>
+      </c>
+      <c r="M13" s="14">
+        <v>0</v>
+      </c>
+      <c r="N13" s="14">
+        <v>0</v>
+      </c>
+      <c r="O13" s="14">
+        <v>0</v>
+      </c>
+      <c r="P13" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="1">
+        <v>0</v>
+      </c>
+      <c r="R13" s="1">
+        <v>0</v>
+      </c>
+      <c r="S13" s="15">
         <v>800</v>
       </c>
-      <c r="M13" s="9">
+      <c r="T13" s="15">
         <v>800</v>
       </c>
-      <c r="N13" s="9">
+      <c r="U13" s="15">
         <v>800</v>
       </c>
-      <c r="O13" s="9">
+      <c r="V13" s="15">
         <v>800</v>
       </c>
-      <c r="P13" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="9">
-        <v>99</v>
-      </c>
-      <c r="R13" s="8">
-        <v>1000000000000</v>
-      </c>
-      <c r="S13" s="8">
-        <v>1000000000000</v>
-      </c>
-    </row>
-    <row r="14" customHeight="1" spans="1:19">
-      <c r="A14" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>35</v>
-      </c>
+      <c r="W13" s="15">
+        <v>30</v>
+      </c>
+      <c r="X13" s="15">
+        <v>0</v>
+      </c>
+      <c r="Y13" s="15">
+        <v>80</v>
+      </c>
+      <c r="Z13" s="15">
+        <v>50</v>
+      </c>
+      <c r="AA13" s="13">
+        <v>400000000000000</v>
+      </c>
+      <c r="AB13" s="13">
+        <v>400000000000000</v>
+      </c>
+    </row>
+    <row r="14" customHeight="1" spans="1:28">
       <c r="C14" s="1">
         <v>9</v>
       </c>
@@ -1857,56 +2828,77 @@
         <f t="shared" si="1"/>
         <v>900</v>
       </c>
-      <c r="F14" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="G14" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="H14" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="I14" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="J14" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="K14" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="L14" s="9">
+      <c r="F14" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="G14" s="14">
+        <v>1</v>
+      </c>
+      <c r="H14" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="I14" s="14">
+        <v>1</v>
+      </c>
+      <c r="J14" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="K14" s="14">
+        <v>1</v>
+      </c>
+      <c r="L14" s="14">
+        <v>0</v>
+      </c>
+      <c r="M14" s="14">
+        <v>0</v>
+      </c>
+      <c r="N14" s="14">
+        <v>0</v>
+      </c>
+      <c r="O14" s="14">
+        <v>0</v>
+      </c>
+      <c r="P14" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="1">
+        <v>0</v>
+      </c>
+      <c r="R14" s="1">
+        <v>0</v>
+      </c>
+      <c r="S14" s="15">
         <v>900</v>
       </c>
-      <c r="M14" s="9">
+      <c r="T14" s="15">
         <v>900</v>
       </c>
-      <c r="N14" s="9">
+      <c r="U14" s="15">
         <v>900</v>
       </c>
-      <c r="O14" s="9">
+      <c r="V14" s="15">
         <v>900</v>
       </c>
-      <c r="P14" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="9">
-        <v>99</v>
-      </c>
-      <c r="R14" s="8">
-        <v>1000000000000</v>
-      </c>
-      <c r="S14" s="8">
-        <v>1000000000000</v>
-      </c>
-    </row>
-    <row r="15" customHeight="1" spans="1:19">
-      <c r="A15" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>35</v>
-      </c>
+      <c r="W14" s="15">
+        <v>40</v>
+      </c>
+      <c r="X14" s="15">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="15">
+        <v>90</v>
+      </c>
+      <c r="Z14" s="15">
+        <v>70</v>
+      </c>
+      <c r="AA14" s="13">
+        <v>800000000000000</v>
+      </c>
+      <c r="AB14" s="13">
+        <v>800000000000000</v>
+      </c>
+    </row>
+    <row r="15" customHeight="1" spans="1:28">
       <c r="C15" s="1">
         <v>10</v>
       </c>
@@ -1918,98 +2910,5233 @@
         <f t="shared" si="1"/>
         <v>1000</v>
       </c>
-      <c r="F15" s="11" t="s">
+      <c r="F15" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="G15" s="14">
+        <v>1</v>
+      </c>
+      <c r="H15" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="I15" s="14">
+        <v>1</v>
+      </c>
+      <c r="J15" s="26" t="s">
+        <v>58</v>
+      </c>
+      <c r="K15" s="14">
+        <v>1</v>
+      </c>
+      <c r="L15" s="14">
+        <v>0</v>
+      </c>
+      <c r="M15" s="14">
+        <v>0</v>
+      </c>
+      <c r="N15" s="14">
+        <v>0</v>
+      </c>
+      <c r="O15" s="14">
+        <v>0</v>
+      </c>
+      <c r="P15" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="1">
+        <v>0</v>
+      </c>
+      <c r="R15" s="1">
+        <v>0</v>
+      </c>
+      <c r="S15" s="15">
+        <v>1000</v>
+      </c>
+      <c r="T15" s="15">
+        <v>1000</v>
+      </c>
+      <c r="U15" s="15">
+        <v>1000</v>
+      </c>
+      <c r="V15" s="15">
+        <v>1000</v>
+      </c>
+      <c r="W15" s="15">
+        <v>50</v>
+      </c>
+      <c r="X15" s="15">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="15">
+        <v>95</v>
+      </c>
+      <c r="Z15" s="15">
+        <v>90</v>
+      </c>
+      <c r="AA15" s="13">
+        <v>1600000000000000</v>
+      </c>
+      <c r="AB15" s="13">
+        <v>1600000000000000</v>
+      </c>
+    </row>
+    <row r="16" customHeight="1" spans="1:28">
+      <c r="C16" s="1">
+        <v>11</v>
+      </c>
+      <c r="D16" s="1">
+        <f t="shared" si="0"/>
+        <v>1001</v>
+      </c>
+      <c r="E16" s="1">
+        <f t="shared" si="1"/>
+        <v>1100</v>
+      </c>
+      <c r="F16" s="26" t="s">
+        <v>59</v>
+      </c>
+      <c r="G16" s="14">
+        <v>0.2</v>
+      </c>
+      <c r="H16" s="26" t="s">
+        <v>60</v>
+      </c>
+      <c r="I16" s="14">
+        <v>0.1</v>
+      </c>
+      <c r="J16" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="K16" s="14">
+        <v>1</v>
+      </c>
+      <c r="L16" s="14">
+        <v>0</v>
+      </c>
+      <c r="M16" s="14">
+        <v>0</v>
+      </c>
+      <c r="N16" s="14">
+        <v>0</v>
+      </c>
+      <c r="O16" s="14">
+        <v>0</v>
+      </c>
+      <c r="P16" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="1">
+        <v>0</v>
+      </c>
+      <c r="R16" s="1">
+        <v>0</v>
+      </c>
+      <c r="S16" s="15">
+        <f>S15+200</f>
+        <v>1200</v>
+      </c>
+      <c r="T16" s="15">
+        <f t="shared" ref="T16:T25" si="2">T15+200</f>
+        <v>1200</v>
+      </c>
+      <c r="U16" s="15">
+        <f t="shared" ref="U16:U25" si="3">U15+200</f>
+        <v>1200</v>
+      </c>
+      <c r="V16" s="15">
+        <f t="shared" ref="V16:V25" si="4">V15+200</f>
+        <v>1200</v>
+      </c>
+      <c r="W16" s="15">
+        <v>55</v>
+      </c>
+      <c r="X16" s="15">
+        <v>20</v>
+      </c>
+      <c r="Y16" s="15">
+        <v>95</v>
+      </c>
+      <c r="Z16" s="15">
+        <v>90</v>
+      </c>
+      <c r="AA16" s="13">
+        <v>3200000000000000</v>
+      </c>
+      <c r="AB16" s="13">
+        <v>3200000000000000</v>
+      </c>
+    </row>
+    <row r="17" customHeight="1" spans="3:28">
+      <c r="C17" s="1">
+        <v>12</v>
+      </c>
+      <c r="D17" s="1">
+        <f t="shared" si="0"/>
+        <v>1101</v>
+      </c>
+      <c r="E17" s="1">
+        <f t="shared" si="1"/>
+        <v>1200</v>
+      </c>
+      <c r="F17" s="26" t="s">
+        <v>62</v>
+      </c>
+      <c r="G17" s="14">
+        <v>0.2</v>
+      </c>
+      <c r="H17" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="I17" s="14">
+        <v>0.1</v>
+      </c>
+      <c r="J17" s="26" t="s">
+        <v>64</v>
+      </c>
+      <c r="K17" s="14">
+        <v>1</v>
+      </c>
+      <c r="L17" s="14">
+        <v>0</v>
+      </c>
+      <c r="M17" s="14">
+        <v>0</v>
+      </c>
+      <c r="N17" s="14">
+        <v>0</v>
+      </c>
+      <c r="O17" s="14">
+        <v>0</v>
+      </c>
+      <c r="P17" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="1">
+        <v>0</v>
+      </c>
+      <c r="R17" s="1">
+        <v>0</v>
+      </c>
+      <c r="S17" s="15">
+        <f>S16+200</f>
+        <v>1400</v>
+      </c>
+      <c r="T17" s="15">
+        <f t="shared" si="2"/>
+        <v>1400</v>
+      </c>
+      <c r="U17" s="15">
+        <f t="shared" si="3"/>
+        <v>1400</v>
+      </c>
+      <c r="V17" s="15">
+        <f t="shared" si="4"/>
+        <v>1400</v>
+      </c>
+      <c r="W17" s="15">
+        <v>60</v>
+      </c>
+      <c r="X17" s="15">
+        <f t="shared" ref="X17:X40" si="5">X16+5</f>
+        <v>25</v>
+      </c>
+      <c r="Y17" s="15">
+        <v>95</v>
+      </c>
+      <c r="Z17" s="15">
+        <v>90</v>
+      </c>
+      <c r="AA17" s="13">
+        <v>6400000000000000</v>
+      </c>
+      <c r="AB17" s="13">
+        <v>6400000000000000</v>
+      </c>
+    </row>
+    <row r="18" customHeight="1" spans="3:28">
+      <c r="C18" s="1">
+        <v>13</v>
+      </c>
+      <c r="D18" s="1">
+        <f t="shared" si="0"/>
+        <v>1201</v>
+      </c>
+      <c r="E18" s="1">
+        <f t="shared" si="1"/>
+        <v>1300</v>
+      </c>
+      <c r="F18" s="26" t="s">
+        <v>65</v>
+      </c>
+      <c r="G18" s="14">
+        <v>0.2</v>
+      </c>
+      <c r="H18" s="26" t="s">
+        <v>66</v>
+      </c>
+      <c r="I18" s="14">
+        <v>0.1</v>
+      </c>
+      <c r="J18" s="26" t="s">
+        <v>67</v>
+      </c>
+      <c r="K18" s="14">
+        <v>1</v>
+      </c>
+      <c r="L18" s="14">
+        <v>0</v>
+      </c>
+      <c r="M18" s="14">
+        <v>0</v>
+      </c>
+      <c r="N18" s="14">
+        <v>0</v>
+      </c>
+      <c r="O18" s="14">
+        <v>0</v>
+      </c>
+      <c r="P18" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="1">
+        <v>0</v>
+      </c>
+      <c r="R18" s="1">
+        <v>0</v>
+      </c>
+      <c r="S18" s="15">
+        <f>S17+200</f>
+        <v>1600</v>
+      </c>
+      <c r="T18" s="15">
+        <f t="shared" si="2"/>
+        <v>1600</v>
+      </c>
+      <c r="U18" s="15">
+        <f t="shared" si="3"/>
+        <v>1600</v>
+      </c>
+      <c r="V18" s="15">
+        <f t="shared" si="4"/>
+        <v>1600</v>
+      </c>
+      <c r="W18" s="15">
+        <v>65</v>
+      </c>
+      <c r="X18" s="15">
+        <f t="shared" si="5"/>
+        <v>30</v>
+      </c>
+      <c r="Y18" s="15">
+        <v>95</v>
+      </c>
+      <c r="Z18" s="15">
+        <v>90</v>
+      </c>
+      <c r="AA18" s="13">
+        <v>1e+16</v>
+      </c>
+      <c r="AB18" s="13">
+        <v>1e+16</v>
+      </c>
+    </row>
+    <row r="19" customHeight="1" spans="3:28">
+      <c r="C19" s="1">
+        <v>14</v>
+      </c>
+      <c r="D19" s="1">
+        <f t="shared" si="0"/>
+        <v>1301</v>
+      </c>
+      <c r="E19" s="1">
+        <f t="shared" si="1"/>
+        <v>1400</v>
+      </c>
+      <c r="F19" s="26" t="s">
+        <v>68</v>
+      </c>
+      <c r="G19" s="14">
+        <v>0.2</v>
+      </c>
+      <c r="H19" s="26" t="s">
+        <v>69</v>
+      </c>
+      <c r="I19" s="14">
+        <v>0.1</v>
+      </c>
+      <c r="J19" s="26" t="s">
+        <v>70</v>
+      </c>
+      <c r="K19" s="14">
+        <v>1</v>
+      </c>
+      <c r="L19" s="14">
+        <v>0</v>
+      </c>
+      <c r="M19" s="14">
+        <v>0</v>
+      </c>
+      <c r="N19" s="14">
+        <v>0</v>
+      </c>
+      <c r="O19" s="14">
+        <v>0</v>
+      </c>
+      <c r="P19" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="1">
+        <v>0</v>
+      </c>
+      <c r="R19" s="1">
+        <v>0</v>
+      </c>
+      <c r="S19" s="15">
+        <f>S18+200</f>
+        <v>1800</v>
+      </c>
+      <c r="T19" s="15">
+        <f t="shared" si="2"/>
+        <v>1800</v>
+      </c>
+      <c r="U19" s="15">
+        <f t="shared" si="3"/>
+        <v>1800</v>
+      </c>
+      <c r="V19" s="15">
+        <f t="shared" si="4"/>
+        <v>1800</v>
+      </c>
+      <c r="W19" s="15">
+        <v>70</v>
+      </c>
+      <c r="X19" s="15">
+        <f t="shared" si="5"/>
+        <v>35</v>
+      </c>
+      <c r="Y19" s="15">
+        <v>95</v>
+      </c>
+      <c r="Z19" s="15">
+        <v>90</v>
+      </c>
+      <c r="AA19" s="13">
+        <v>2e+16</v>
+      </c>
+      <c r="AB19" s="13">
+        <v>2e+16</v>
+      </c>
+    </row>
+    <row r="20" customHeight="1" spans="3:28">
+      <c r="C20" s="1">
+        <v>15</v>
+      </c>
+      <c r="D20" s="1">
+        <f t="shared" si="0"/>
+        <v>1401</v>
+      </c>
+      <c r="E20" s="1">
+        <f t="shared" si="1"/>
+        <v>1500</v>
+      </c>
+      <c r="F20" s="26" t="s">
+        <v>71</v>
+      </c>
+      <c r="G20" s="14">
+        <v>0.2</v>
+      </c>
+      <c r="H20" s="26" t="s">
+        <v>72</v>
+      </c>
+      <c r="I20" s="14">
+        <v>0.1</v>
+      </c>
+      <c r="J20" s="26" t="s">
+        <v>73</v>
+      </c>
+      <c r="K20" s="14">
+        <v>1</v>
+      </c>
+      <c r="L20" s="14">
+        <v>0</v>
+      </c>
+      <c r="M20" s="14">
+        <v>0</v>
+      </c>
+      <c r="N20" s="14">
+        <v>0</v>
+      </c>
+      <c r="O20" s="14">
+        <v>0</v>
+      </c>
+      <c r="P20" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="1">
+        <v>0</v>
+      </c>
+      <c r="R20" s="1">
+        <v>0</v>
+      </c>
+      <c r="S20" s="15">
+        <f>S19+200</f>
+        <v>2000</v>
+      </c>
+      <c r="T20" s="15">
+        <f t="shared" si="2"/>
+        <v>2000</v>
+      </c>
+      <c r="U20" s="15">
+        <f t="shared" si="3"/>
+        <v>2000</v>
+      </c>
+      <c r="V20" s="15">
+        <f t="shared" si="4"/>
+        <v>2000</v>
+      </c>
+      <c r="W20" s="15">
+        <v>75</v>
+      </c>
+      <c r="X20" s="15">
+        <f t="shared" si="5"/>
+        <v>40</v>
+      </c>
+      <c r="Y20" s="15">
+        <v>95</v>
+      </c>
+      <c r="Z20" s="15">
+        <v>90</v>
+      </c>
+      <c r="AA20" s="13">
+        <v>3e+16</v>
+      </c>
+      <c r="AB20" s="13">
+        <v>3e+16</v>
+      </c>
+    </row>
+    <row r="21" customHeight="1" spans="3:28">
+      <c r="C21" s="1">
+        <v>16</v>
+      </c>
+      <c r="D21" s="1">
+        <f t="shared" si="0"/>
+        <v>1501</v>
+      </c>
+      <c r="E21" s="1">
+        <f t="shared" si="1"/>
+        <v>1600</v>
+      </c>
+      <c r="F21" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="G21" s="14">
+        <v>0.1</v>
+      </c>
+      <c r="H21" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="I21" s="14">
+        <v>1</v>
+      </c>
+      <c r="J21" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="K21" s="14">
+        <v>10</v>
+      </c>
+      <c r="L21" s="14">
+        <v>100</v>
+      </c>
+      <c r="M21" s="14">
+        <v>0.2</v>
+      </c>
+      <c r="N21" s="14">
+        <v>0</v>
+      </c>
+      <c r="O21" s="14">
+        <v>0</v>
+      </c>
+      <c r="P21" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="1">
+        <v>0</v>
+      </c>
+      <c r="R21" s="1">
+        <v>0</v>
+      </c>
+      <c r="S21" s="15">
+        <f>S20+500</f>
+        <v>2500</v>
+      </c>
+      <c r="T21" s="15">
+        <f>T20+500</f>
+        <v>2500</v>
+      </c>
+      <c r="U21" s="15">
+        <f t="shared" ref="U21:U35" si="6">U20+500</f>
+        <v>2500</v>
+      </c>
+      <c r="V21" s="15">
+        <f t="shared" ref="V21:V35" si="7">V20+500</f>
+        <v>2500</v>
+      </c>
+      <c r="W21" s="15">
+        <f t="shared" ref="W21:W40" si="8">W20+5</f>
+        <v>80</v>
+      </c>
+      <c r="X21" s="15">
+        <f t="shared" si="5"/>
+        <v>45</v>
+      </c>
+      <c r="Y21" s="15">
+        <v>95</v>
+      </c>
+      <c r="Z21" s="15">
+        <v>95</v>
+      </c>
+      <c r="AA21" s="13">
+        <v>4e+16</v>
+      </c>
+      <c r="AB21" s="13">
+        <v>4e+16</v>
+      </c>
+    </row>
+    <row r="22" customHeight="1" spans="3:28">
+      <c r="C22" s="1">
+        <v>17</v>
+      </c>
+      <c r="D22" s="1">
+        <f t="shared" si="0"/>
+        <v>1601</v>
+      </c>
+      <c r="E22" s="1">
+        <f t="shared" si="1"/>
+        <v>1700</v>
+      </c>
+      <c r="F22" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="G22" s="14">
+        <v>0.1</v>
+      </c>
+      <c r="H22" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="I22" s="14">
+        <v>1</v>
+      </c>
+      <c r="J22" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="K22" s="14">
+        <v>10</v>
+      </c>
+      <c r="L22" s="14">
+        <v>2000</v>
+      </c>
+      <c r="M22" s="14">
+        <v>0.2</v>
+      </c>
+      <c r="N22" s="14">
+        <v>0</v>
+      </c>
+      <c r="O22" s="14">
+        <v>0</v>
+      </c>
+      <c r="P22" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="1">
+        <v>0</v>
+      </c>
+      <c r="R22" s="1">
+        <v>0</v>
+      </c>
+      <c r="S22" s="15">
+        <f t="shared" ref="S22:S35" si="9">S21+1000</f>
+        <v>3500</v>
+      </c>
+      <c r="T22" s="15">
+        <f t="shared" ref="T22:T35" si="10">T21+1000</f>
+        <v>3500</v>
+      </c>
+      <c r="U22" s="15">
+        <f t="shared" si="6"/>
+        <v>3000</v>
+      </c>
+      <c r="V22" s="15">
+        <f t="shared" si="7"/>
+        <v>3000</v>
+      </c>
+      <c r="W22" s="15">
+        <f t="shared" si="8"/>
+        <v>85</v>
+      </c>
+      <c r="X22" s="15">
+        <f t="shared" si="5"/>
+        <v>50</v>
+      </c>
+      <c r="Y22" s="15">
+        <v>95</v>
+      </c>
+      <c r="Z22" s="15">
+        <v>95</v>
+      </c>
+      <c r="AA22" s="13">
+        <v>5e+16</v>
+      </c>
+      <c r="AB22" s="13">
+        <v>5e+16</v>
+      </c>
+    </row>
+    <row r="23" customHeight="1" spans="3:28">
+      <c r="C23" s="1">
+        <v>18</v>
+      </c>
+      <c r="D23" s="1">
+        <f t="shared" si="0"/>
+        <v>1701</v>
+      </c>
+      <c r="E23" s="1">
+        <f t="shared" si="1"/>
+        <v>1800</v>
+      </c>
+      <c r="F23" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="G23" s="14">
+        <v>0.1</v>
+      </c>
+      <c r="H23" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="I23" s="14">
+        <v>1</v>
+      </c>
+      <c r="J23" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="K23" s="14">
+        <v>10</v>
+      </c>
+      <c r="L23" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="M23" s="14">
+        <v>0.2</v>
+      </c>
+      <c r="N23" s="14">
+        <v>0</v>
+      </c>
+      <c r="O23" s="14">
+        <v>0</v>
+      </c>
+      <c r="P23" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="1">
+        <v>0</v>
+      </c>
+      <c r="R23" s="1">
+        <v>0</v>
+      </c>
+      <c r="S23" s="15">
+        <f t="shared" si="9"/>
+        <v>4500</v>
+      </c>
+      <c r="T23" s="15">
+        <f t="shared" si="10"/>
+        <v>4500</v>
+      </c>
+      <c r="U23" s="15">
+        <f t="shared" si="6"/>
+        <v>3500</v>
+      </c>
+      <c r="V23" s="15">
+        <f t="shared" si="7"/>
+        <v>3500</v>
+      </c>
+      <c r="W23" s="15">
+        <f t="shared" si="8"/>
+        <v>90</v>
+      </c>
+      <c r="X23" s="15">
+        <f t="shared" si="5"/>
+        <v>55</v>
+      </c>
+      <c r="Y23" s="15">
+        <v>95</v>
+      </c>
+      <c r="Z23" s="15">
+        <v>95</v>
+      </c>
+      <c r="AA23" s="13">
+        <v>6e+16</v>
+      </c>
+      <c r="AB23" s="13">
+        <v>6e+16</v>
+      </c>
+    </row>
+    <row r="24" customHeight="1" spans="3:28">
+      <c r="C24" s="1">
+        <v>19</v>
+      </c>
+      <c r="D24" s="1">
+        <f t="shared" si="0"/>
+        <v>1801</v>
+      </c>
+      <c r="E24" s="1">
+        <f t="shared" si="1"/>
+        <v>1900</v>
+      </c>
+      <c r="F24" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="G24" s="14">
+        <v>0.1</v>
+      </c>
+      <c r="H24" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="I24" s="14">
+        <v>1</v>
+      </c>
+      <c r="J24" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="K24" s="14">
+        <v>10</v>
+      </c>
+      <c r="L24" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="M24" s="14">
+        <v>0.2</v>
+      </c>
+      <c r="N24" s="14">
+        <v>0</v>
+      </c>
+      <c r="O24" s="14">
+        <v>0</v>
+      </c>
+      <c r="P24" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="1">
+        <v>0</v>
+      </c>
+      <c r="R24" s="1">
+        <v>0</v>
+      </c>
+      <c r="S24" s="15">
+        <f t="shared" si="9"/>
+        <v>5500</v>
+      </c>
+      <c r="T24" s="15">
+        <f t="shared" si="10"/>
+        <v>5500</v>
+      </c>
+      <c r="U24" s="15">
+        <f t="shared" si="6"/>
+        <v>4000</v>
+      </c>
+      <c r="V24" s="15">
+        <f t="shared" si="7"/>
+        <v>4000</v>
+      </c>
+      <c r="W24" s="15">
+        <f t="shared" si="8"/>
+        <v>95</v>
+      </c>
+      <c r="X24" s="15">
+        <f t="shared" si="5"/>
+        <v>60</v>
+      </c>
+      <c r="Y24" s="15">
+        <v>95</v>
+      </c>
+      <c r="Z24" s="15">
+        <v>95</v>
+      </c>
+      <c r="AA24" s="13">
+        <v>7e+16</v>
+      </c>
+      <c r="AB24" s="13">
+        <v>7e+16</v>
+      </c>
+    </row>
+    <row r="25" customHeight="1" spans="3:28">
+      <c r="C25" s="1">
+        <v>20</v>
+      </c>
+      <c r="D25" s="1">
+        <f t="shared" si="0"/>
+        <v>1901</v>
+      </c>
+      <c r="E25" s="1">
+        <f t="shared" si="1"/>
+        <v>2000</v>
+      </c>
+      <c r="F25" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="G25" s="14">
+        <v>0.1</v>
+      </c>
+      <c r="H25" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="I25" s="14">
+        <v>1</v>
+      </c>
+      <c r="J25" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="K25" s="14">
+        <v>10</v>
+      </c>
+      <c r="L25" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="M25" s="14">
+        <v>0.2</v>
+      </c>
+      <c r="N25" s="14">
+        <v>0</v>
+      </c>
+      <c r="O25" s="14">
+        <v>0</v>
+      </c>
+      <c r="P25" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="1">
+        <v>0</v>
+      </c>
+      <c r="R25" s="1">
+        <v>0</v>
+      </c>
+      <c r="S25" s="15">
+        <f t="shared" si="9"/>
+        <v>6500</v>
+      </c>
+      <c r="T25" s="15">
+        <f t="shared" si="10"/>
+        <v>6500</v>
+      </c>
+      <c r="U25" s="15">
+        <f t="shared" si="6"/>
+        <v>4500</v>
+      </c>
+      <c r="V25" s="15">
+        <f t="shared" si="7"/>
+        <v>4500</v>
+      </c>
+      <c r="W25" s="15">
+        <f t="shared" si="8"/>
+        <v>100</v>
+      </c>
+      <c r="X25" s="15">
+        <f t="shared" si="5"/>
+        <v>65</v>
+      </c>
+      <c r="Y25" s="15">
+        <v>95</v>
+      </c>
+      <c r="Z25" s="15">
+        <v>95</v>
+      </c>
+      <c r="AA25" s="13">
+        <v>8e+16</v>
+      </c>
+      <c r="AB25" s="13">
+        <v>8e+16</v>
+      </c>
+    </row>
+    <row r="26" s="2" customFormat="1" customHeight="1" spans="3:28">
+      <c r="C26" s="16">
+        <v>21</v>
+      </c>
+      <c r="D26" s="16">
+        <f t="shared" si="0"/>
+        <v>2001</v>
+      </c>
+      <c r="E26" s="16">
+        <f t="shared" si="1"/>
+        <v>2100</v>
+      </c>
+      <c r="F26" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="G26" s="14">
+        <v>0.1</v>
+      </c>
+      <c r="H26" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="I26" s="18">
+        <v>1</v>
+      </c>
+      <c r="J26" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="K26" s="18">
+        <v>10</v>
+      </c>
+      <c r="L26" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="M26" s="14">
+        <v>0.2</v>
+      </c>
+      <c r="N26" s="14">
+        <v>0</v>
+      </c>
+      <c r="O26" s="14">
+        <v>0</v>
+      </c>
+      <c r="P26" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="1">
+        <v>0</v>
+      </c>
+      <c r="R26" s="1">
+        <v>0</v>
+      </c>
+      <c r="S26" s="2">
+        <f t="shared" si="9"/>
+        <v>7500</v>
+      </c>
+      <c r="T26" s="2">
+        <f t="shared" si="10"/>
+        <v>7500</v>
+      </c>
+      <c r="U26" s="2">
+        <f t="shared" si="6"/>
+        <v>5000</v>
+      </c>
+      <c r="V26" s="2">
+        <f t="shared" si="7"/>
+        <v>5000</v>
+      </c>
+      <c r="W26" s="2">
+        <f t="shared" si="8"/>
+        <v>105</v>
+      </c>
+      <c r="X26" s="2">
+        <f t="shared" si="5"/>
+        <v>70</v>
+      </c>
+      <c r="Y26" s="2">
+        <v>95</v>
+      </c>
+      <c r="Z26" s="15">
+        <v>99</v>
+      </c>
+      <c r="AA26" s="17">
+        <v>9e+16</v>
+      </c>
+      <c r="AB26" s="17">
+        <v>9e+16</v>
+      </c>
+    </row>
+    <row r="27" customHeight="1" spans="3:28">
+      <c r="C27" s="1">
+        <v>22</v>
+      </c>
+      <c r="D27" s="1">
+        <f t="shared" si="0"/>
+        <v>2101</v>
+      </c>
+      <c r="E27" s="1">
+        <f t="shared" si="1"/>
+        <v>2200</v>
+      </c>
+      <c r="F27" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="G27" s="14">
+        <v>0.1</v>
+      </c>
+      <c r="H27" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="I27" s="14">
+        <v>1</v>
+      </c>
+      <c r="J27" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="K27" s="14">
+        <v>10</v>
+      </c>
+      <c r="L27" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="M27" s="14">
+        <v>0.2</v>
+      </c>
+      <c r="N27" s="14">
+        <v>0</v>
+      </c>
+      <c r="O27" s="14">
+        <v>0</v>
+      </c>
+      <c r="P27" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="1">
+        <v>0</v>
+      </c>
+      <c r="R27" s="1">
+        <v>0</v>
+      </c>
+      <c r="S27" s="15">
+        <f t="shared" si="9"/>
+        <v>8500</v>
+      </c>
+      <c r="T27" s="15">
+        <f t="shared" si="10"/>
+        <v>8500</v>
+      </c>
+      <c r="U27" s="15">
+        <f t="shared" si="6"/>
+        <v>5500</v>
+      </c>
+      <c r="V27" s="15">
+        <f t="shared" si="7"/>
+        <v>5500</v>
+      </c>
+      <c r="W27" s="15">
+        <f t="shared" si="8"/>
+        <v>110</v>
+      </c>
+      <c r="X27" s="15">
+        <f t="shared" si="5"/>
+        <v>75</v>
+      </c>
+      <c r="Y27" s="15">
+        <v>95</v>
+      </c>
+      <c r="Z27" s="15">
+        <v>99.1</v>
+      </c>
+      <c r="AA27" s="13">
+        <v>1e+17</v>
+      </c>
+      <c r="AB27" s="13">
+        <v>1e+17</v>
+      </c>
+    </row>
+    <row r="28" customHeight="1" spans="3:28">
+      <c r="C28" s="1">
+        <v>23</v>
+      </c>
+      <c r="D28" s="1">
+        <f t="shared" si="0"/>
+        <v>2201</v>
+      </c>
+      <c r="E28" s="1">
+        <f t="shared" si="1"/>
+        <v>2300</v>
+      </c>
+      <c r="F28" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="G28" s="14">
+        <v>0.1</v>
+      </c>
+      <c r="H28" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="I28" s="14">
+        <v>1</v>
+      </c>
+      <c r="J28" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="K28" s="14">
+        <v>10</v>
+      </c>
+      <c r="L28" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="M28" s="14">
+        <v>0.2</v>
+      </c>
+      <c r="N28" s="14">
+        <v>0</v>
+      </c>
+      <c r="O28" s="14">
+        <v>0</v>
+      </c>
+      <c r="P28" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="1">
+        <v>0</v>
+      </c>
+      <c r="R28" s="1">
+        <v>0</v>
+      </c>
+      <c r="S28" s="15">
+        <f t="shared" si="9"/>
+        <v>9500</v>
+      </c>
+      <c r="T28" s="15">
+        <f t="shared" si="10"/>
+        <v>9500</v>
+      </c>
+      <c r="U28" s="15">
+        <f t="shared" si="6"/>
+        <v>6000</v>
+      </c>
+      <c r="V28" s="15">
+        <f t="shared" si="7"/>
+        <v>6000</v>
+      </c>
+      <c r="W28" s="15">
+        <f t="shared" si="8"/>
+        <v>115</v>
+      </c>
+      <c r="X28" s="15">
+        <f t="shared" si="5"/>
+        <v>80</v>
+      </c>
+      <c r="Y28" s="15">
+        <v>95</v>
+      </c>
+      <c r="Z28" s="15">
+        <v>99.2</v>
+      </c>
+      <c r="AA28" s="13">
+        <v>1.1e+17</v>
+      </c>
+      <c r="AB28" s="13">
+        <v>1.1e+17</v>
+      </c>
+    </row>
+    <row r="29" customHeight="1" spans="3:28">
+      <c r="C29" s="1">
+        <v>24</v>
+      </c>
+      <c r="D29" s="1">
+        <f t="shared" si="0"/>
+        <v>2301</v>
+      </c>
+      <c r="E29" s="1">
+        <f t="shared" si="1"/>
+        <v>2400</v>
+      </c>
+      <c r="F29" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="G29" s="14">
+        <v>0.1</v>
+      </c>
+      <c r="H29" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="I29" s="14">
+        <v>1</v>
+      </c>
+      <c r="J29" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="K29" s="14">
+        <v>10</v>
+      </c>
+      <c r="L29" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="M29" s="14">
+        <v>0.2</v>
+      </c>
+      <c r="N29" s="14">
+        <v>0</v>
+      </c>
+      <c r="O29" s="14">
+        <v>0</v>
+      </c>
+      <c r="P29" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="1">
+        <v>0</v>
+      </c>
+      <c r="R29" s="1">
+        <v>0</v>
+      </c>
+      <c r="S29" s="15">
+        <f t="shared" si="9"/>
+        <v>10500</v>
+      </c>
+      <c r="T29" s="15">
+        <f t="shared" si="10"/>
+        <v>10500</v>
+      </c>
+      <c r="U29" s="15">
+        <f t="shared" si="6"/>
+        <v>6500</v>
+      </c>
+      <c r="V29" s="15">
+        <f t="shared" si="7"/>
+        <v>6500</v>
+      </c>
+      <c r="W29" s="15">
+        <f t="shared" si="8"/>
+        <v>120</v>
+      </c>
+      <c r="X29" s="15">
+        <f t="shared" si="5"/>
+        <v>85</v>
+      </c>
+      <c r="Y29" s="15">
+        <v>95</v>
+      </c>
+      <c r="Z29" s="15">
+        <v>99.3</v>
+      </c>
+      <c r="AA29" s="13">
+        <v>1.2e+17</v>
+      </c>
+      <c r="AB29" s="13">
+        <v>1.2e+17</v>
+      </c>
+    </row>
+    <row r="30" customHeight="1" spans="3:28">
+      <c r="C30" s="1">
+        <v>25</v>
+      </c>
+      <c r="D30" s="1">
+        <f t="shared" si="0"/>
+        <v>2401</v>
+      </c>
+      <c r="E30" s="1">
+        <f t="shared" si="1"/>
+        <v>2500</v>
+      </c>
+      <c r="F30" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="G30" s="14">
+        <v>0.1</v>
+      </c>
+      <c r="H30" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="I30" s="14">
+        <v>1</v>
+      </c>
+      <c r="J30" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="K30" s="14">
+        <v>10</v>
+      </c>
+      <c r="L30" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="M30" s="14">
+        <v>0.2</v>
+      </c>
+      <c r="N30" s="14">
+        <v>0</v>
+      </c>
+      <c r="O30" s="14">
+        <v>0</v>
+      </c>
+      <c r="P30" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="1">
+        <v>0</v>
+      </c>
+      <c r="R30" s="1">
+        <v>0</v>
+      </c>
+      <c r="S30" s="15">
+        <f t="shared" si="9"/>
+        <v>11500</v>
+      </c>
+      <c r="T30" s="15">
+        <f t="shared" si="10"/>
+        <v>11500</v>
+      </c>
+      <c r="U30" s="15">
+        <f t="shared" si="6"/>
+        <v>7000</v>
+      </c>
+      <c r="V30" s="15">
+        <f t="shared" si="7"/>
+        <v>7000</v>
+      </c>
+      <c r="W30" s="15">
+        <f t="shared" si="8"/>
+        <v>125</v>
+      </c>
+      <c r="X30" s="15">
+        <f t="shared" si="5"/>
+        <v>90</v>
+      </c>
+      <c r="Y30" s="15">
+        <v>95</v>
+      </c>
+      <c r="Z30" s="15">
+        <v>99.4</v>
+      </c>
+      <c r="AA30" s="13">
+        <v>1.3e+17</v>
+      </c>
+      <c r="AB30" s="13">
+        <v>1.3e+17</v>
+      </c>
+    </row>
+    <row r="31" customHeight="1" spans="3:28">
+      <c r="C31" s="1">
+        <v>26</v>
+      </c>
+      <c r="D31" s="1">
+        <f t="shared" si="0"/>
+        <v>2501</v>
+      </c>
+      <c r="E31" s="1">
+        <f t="shared" si="1"/>
+        <v>2600</v>
+      </c>
+      <c r="F31" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="G31" s="14">
+        <v>0.1</v>
+      </c>
+      <c r="H31" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="I31" s="14">
+        <v>1</v>
+      </c>
+      <c r="J31" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="K31" s="14">
+        <v>10</v>
+      </c>
+      <c r="L31" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="M31" s="14">
+        <v>0.2</v>
+      </c>
+      <c r="N31" s="14">
+        <v>0</v>
+      </c>
+      <c r="O31" s="14">
+        <v>0</v>
+      </c>
+      <c r="P31" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="1">
+        <v>0</v>
+      </c>
+      <c r="R31" s="1">
+        <v>0</v>
+      </c>
+      <c r="S31" s="15">
+        <f t="shared" ref="S31:S40" si="11">S30+1500</f>
+        <v>13000</v>
+      </c>
+      <c r="T31" s="15">
+        <f t="shared" ref="T31:T40" si="12">T30+1500</f>
+        <v>13000</v>
+      </c>
+      <c r="U31" s="15">
+        <f t="shared" ref="U31:U40" si="13">U30+1000</f>
+        <v>8000</v>
+      </c>
+      <c r="V31" s="15">
+        <f t="shared" ref="V31:V40" si="14">V30+1000</f>
+        <v>8000</v>
+      </c>
+      <c r="W31" s="15">
+        <f t="shared" si="8"/>
+        <v>130</v>
+      </c>
+      <c r="X31" s="15">
+        <f t="shared" si="5"/>
+        <v>95</v>
+      </c>
+      <c r="Y31" s="15">
+        <v>99</v>
+      </c>
+      <c r="Z31" s="15">
+        <v>99.6</v>
+      </c>
+      <c r="AA31" s="13">
+        <v>1.4e+17</v>
+      </c>
+      <c r="AB31" s="13">
+        <v>1.4e+17</v>
+      </c>
+    </row>
+    <row r="32" customHeight="1" spans="3:28">
+      <c r="C32" s="1">
+        <v>27</v>
+      </c>
+      <c r="D32" s="1">
+        <f t="shared" si="0"/>
+        <v>2601</v>
+      </c>
+      <c r="E32" s="1">
+        <f t="shared" si="1"/>
+        <v>2700</v>
+      </c>
+      <c r="F32" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="G32" s="14">
+        <v>0.1</v>
+      </c>
+      <c r="H32" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="I32" s="14">
+        <v>1</v>
+      </c>
+      <c r="J32" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="K32" s="14">
+        <v>10</v>
+      </c>
+      <c r="L32" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="M32" s="14">
+        <v>0.2</v>
+      </c>
+      <c r="N32" s="14">
+        <v>0</v>
+      </c>
+      <c r="O32" s="14">
+        <v>0</v>
+      </c>
+      <c r="P32" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="1">
+        <v>0</v>
+      </c>
+      <c r="R32" s="1">
+        <v>0</v>
+      </c>
+      <c r="S32" s="15">
+        <f t="shared" si="11"/>
+        <v>14500</v>
+      </c>
+      <c r="T32" s="15">
+        <f t="shared" si="12"/>
+        <v>14500</v>
+      </c>
+      <c r="U32" s="15">
+        <f t="shared" si="13"/>
+        <v>9000</v>
+      </c>
+      <c r="V32" s="15">
+        <f t="shared" si="14"/>
+        <v>9000</v>
+      </c>
+      <c r="W32" s="15">
+        <f t="shared" si="8"/>
+        <v>135</v>
+      </c>
+      <c r="X32" s="15">
+        <f t="shared" si="5"/>
+        <v>100</v>
+      </c>
+      <c r="Y32" s="15">
+        <v>99.1</v>
+      </c>
+      <c r="Z32" s="15">
+        <v>99.9</v>
+      </c>
+      <c r="AA32" s="13">
+        <v>1.5e+17</v>
+      </c>
+      <c r="AB32" s="13">
+        <v>1.5e+17</v>
+      </c>
+    </row>
+    <row r="33" customHeight="1" spans="3:28">
+      <c r="C33" s="1">
+        <v>28</v>
+      </c>
+      <c r="D33" s="1">
+        <f t="shared" si="0"/>
+        <v>2701</v>
+      </c>
+      <c r="E33" s="1">
+        <f t="shared" si="1"/>
+        <v>2800</v>
+      </c>
+      <c r="F33" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="G33" s="14">
+        <v>0.1</v>
+      </c>
+      <c r="H33" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="I33" s="14">
+        <v>1</v>
+      </c>
+      <c r="J33" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="K33" s="14">
+        <v>10</v>
+      </c>
+      <c r="L33" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="M33" s="14">
+        <v>0.2</v>
+      </c>
+      <c r="N33" s="14">
+        <v>0</v>
+      </c>
+      <c r="O33" s="14">
+        <v>0</v>
+      </c>
+      <c r="P33" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q33" s="1">
+        <v>0</v>
+      </c>
+      <c r="R33" s="1">
+        <v>0</v>
+      </c>
+      <c r="S33" s="15">
+        <f t="shared" si="11"/>
+        <v>16000</v>
+      </c>
+      <c r="T33" s="15">
+        <f t="shared" si="12"/>
+        <v>16000</v>
+      </c>
+      <c r="U33" s="15">
+        <f t="shared" si="13"/>
+        <v>10000</v>
+      </c>
+      <c r="V33" s="15">
+        <f t="shared" si="14"/>
+        <v>10000</v>
+      </c>
+      <c r="W33" s="15">
+        <f t="shared" si="8"/>
+        <v>140</v>
+      </c>
+      <c r="X33" s="15">
+        <f t="shared" si="5"/>
+        <v>105</v>
+      </c>
+      <c r="Y33" s="15">
+        <v>99.2</v>
+      </c>
+      <c r="Z33" s="15">
+        <v>99.93</v>
+      </c>
+      <c r="AA33" s="13">
+        <v>1.6e+17</v>
+      </c>
+      <c r="AB33" s="13">
+        <v>1.6e+17</v>
+      </c>
+    </row>
+    <row r="34" customHeight="1" spans="3:28">
+      <c r="C34" s="1">
+        <v>29</v>
+      </c>
+      <c r="D34" s="1">
+        <f t="shared" si="0"/>
+        <v>2801</v>
+      </c>
+      <c r="E34" s="1">
+        <f t="shared" si="1"/>
+        <v>2900</v>
+      </c>
+      <c r="F34" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="G34" s="14">
+        <v>0.1</v>
+      </c>
+      <c r="H34" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="I34" s="14">
+        <v>1</v>
+      </c>
+      <c r="J34" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="K34" s="14">
+        <v>10</v>
+      </c>
+      <c r="L34" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="M34" s="14">
+        <v>0.2</v>
+      </c>
+      <c r="N34" s="14">
+        <v>0</v>
+      </c>
+      <c r="O34" s="14">
+        <v>0</v>
+      </c>
+      <c r="P34" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="1">
+        <v>0</v>
+      </c>
+      <c r="R34" s="1">
+        <v>0</v>
+      </c>
+      <c r="S34" s="15">
+        <f t="shared" si="11"/>
+        <v>17500</v>
+      </c>
+      <c r="T34" s="15">
+        <f t="shared" si="12"/>
+        <v>17500</v>
+      </c>
+      <c r="U34" s="15">
+        <f t="shared" si="13"/>
+        <v>11000</v>
+      </c>
+      <c r="V34" s="15">
+        <f t="shared" si="14"/>
+        <v>11000</v>
+      </c>
+      <c r="W34" s="15">
+        <f t="shared" si="8"/>
+        <v>145</v>
+      </c>
+      <c r="X34" s="15">
+        <f t="shared" si="5"/>
+        <v>110</v>
+      </c>
+      <c r="Y34" s="15">
+        <v>99.3</v>
+      </c>
+      <c r="Z34" s="15">
+        <v>99.96</v>
+      </c>
+      <c r="AA34" s="13">
+        <v>1.7e+17</v>
+      </c>
+      <c r="AB34" s="13">
+        <v>1.7e+17</v>
+      </c>
+    </row>
+    <row r="35" customHeight="1" spans="3:28">
+      <c r="C35" s="1">
+        <v>30</v>
+      </c>
+      <c r="D35" s="1">
+        <f t="shared" si="0"/>
+        <v>2901</v>
+      </c>
+      <c r="E35" s="1">
+        <f t="shared" si="1"/>
+        <v>3000</v>
+      </c>
+      <c r="F35" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="G35" s="14">
+        <v>0.1</v>
+      </c>
+      <c r="H35" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="I35" s="14">
+        <v>1</v>
+      </c>
+      <c r="J35" s="13" t="s">
+        <v>125</v>
+      </c>
+      <c r="K35" s="14">
+        <v>10</v>
+      </c>
+      <c r="L35" s="14" t="s">
+        <v>126</v>
+      </c>
+      <c r="M35" s="14">
+        <v>0.2</v>
+      </c>
+      <c r="N35" s="14">
+        <v>0</v>
+      </c>
+      <c r="O35" s="14">
+        <v>0</v>
+      </c>
+      <c r="P35" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q35" s="1">
+        <v>0</v>
+      </c>
+      <c r="R35" s="1">
+        <v>0</v>
+      </c>
+      <c r="S35" s="15">
+        <f t="shared" si="11"/>
+        <v>19000</v>
+      </c>
+      <c r="T35" s="15">
+        <f t="shared" si="12"/>
+        <v>19000</v>
+      </c>
+      <c r="U35" s="15">
+        <f t="shared" si="13"/>
+        <v>12000</v>
+      </c>
+      <c r="V35" s="15">
+        <f t="shared" si="14"/>
+        <v>12000</v>
+      </c>
+      <c r="W35" s="15">
+        <f t="shared" si="8"/>
+        <v>150</v>
+      </c>
+      <c r="X35" s="15">
+        <f t="shared" si="5"/>
+        <v>115</v>
+      </c>
+      <c r="Y35" s="15">
+        <v>99.4</v>
+      </c>
+      <c r="Z35" s="15">
+        <v>99.99</v>
+      </c>
+      <c r="AA35" s="13">
+        <v>1.8e+17</v>
+      </c>
+      <c r="AB35" s="13">
+        <v>1.8e+17</v>
+      </c>
+    </row>
+    <row r="36" customHeight="1" spans="3:28">
+      <c r="C36" s="1">
+        <v>31</v>
+      </c>
+      <c r="D36" s="1">
+        <f t="shared" si="0"/>
+        <v>3001</v>
+      </c>
+      <c r="E36" s="1">
+        <f t="shared" si="1"/>
+        <v>3100</v>
+      </c>
+      <c r="F36" s="13" t="s">
+        <v>127</v>
+      </c>
+      <c r="G36" s="14">
+        <v>0.1</v>
+      </c>
+      <c r="H36" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="I36" s="14">
+        <v>10</v>
+      </c>
+      <c r="J36" s="13" t="s">
+        <v>129</v>
+      </c>
+      <c r="K36" s="14">
+        <v>10</v>
+      </c>
+      <c r="L36" s="14" t="s">
+        <v>130</v>
+      </c>
+      <c r="M36" s="14">
+        <v>10</v>
+      </c>
+      <c r="N36" s="14">
+        <v>10</v>
+      </c>
+      <c r="O36" s="14">
+        <v>0.1</v>
+      </c>
+      <c r="P36" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q36" s="1">
+        <v>0</v>
+      </c>
+      <c r="R36" s="1">
+        <v>0</v>
+      </c>
+      <c r="S36" s="15">
+        <f t="shared" ref="S36:S65" si="15">S35+3000</f>
+        <v>22000</v>
+      </c>
+      <c r="T36" s="15">
+        <f t="shared" ref="T36:T65" si="16">T35+3000</f>
+        <v>22000</v>
+      </c>
+      <c r="U36" s="15">
+        <f t="shared" ref="U36:U65" si="17">U35+2000</f>
+        <v>14000</v>
+      </c>
+      <c r="V36" s="15">
+        <f t="shared" ref="V36:V65" si="18">V35+2000</f>
+        <v>14000</v>
+      </c>
+      <c r="W36" s="15">
+        <f>W35+15</f>
+        <v>165</v>
+      </c>
+      <c r="X36" s="15">
+        <f t="shared" ref="X36:X65" si="19">X35+15</f>
+        <v>130</v>
+      </c>
+      <c r="Y36" s="15">
+        <v>99.4</v>
+      </c>
+      <c r="Z36" s="15">
+        <v>99.999</v>
+      </c>
+      <c r="AA36" s="13">
+        <v>1.9e+17</v>
+      </c>
+      <c r="AB36" s="13">
+        <v>1.9e+17</v>
+      </c>
+    </row>
+    <row r="37" customHeight="1" spans="3:28">
+      <c r="C37" s="1">
+        <v>32</v>
+      </c>
+      <c r="D37" s="1">
+        <f t="shared" si="0"/>
+        <v>3101</v>
+      </c>
+      <c r="E37" s="1">
+        <f t="shared" si="1"/>
+        <v>3200</v>
+      </c>
+      <c r="F37" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="G37" s="14">
+        <v>0.1</v>
+      </c>
+      <c r="H37" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="I37" s="14">
+        <v>10</v>
+      </c>
+      <c r="J37" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="K37" s="14">
+        <v>10</v>
+      </c>
+      <c r="L37" s="14" t="s">
+        <v>134</v>
+      </c>
+      <c r="M37" s="14">
+        <v>10</v>
+      </c>
+      <c r="N37" s="14">
+        <v>100</v>
+      </c>
+      <c r="O37" s="14">
+        <v>0.1</v>
+      </c>
+      <c r="P37" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q37" s="1">
+        <v>0</v>
+      </c>
+      <c r="R37" s="1">
+        <v>0</v>
+      </c>
+      <c r="S37" s="15">
+        <f t="shared" si="15"/>
+        <v>25000</v>
+      </c>
+      <c r="T37" s="15">
+        <f t="shared" si="16"/>
+        <v>25000</v>
+      </c>
+      <c r="U37" s="15">
+        <f t="shared" si="17"/>
+        <v>16000</v>
+      </c>
+      <c r="V37" s="15">
+        <f t="shared" si="18"/>
+        <v>16000</v>
+      </c>
+      <c r="W37" s="15">
+        <f t="shared" ref="W37:W65" si="20">W36+20</f>
+        <v>185</v>
+      </c>
+      <c r="X37" s="15">
+        <f t="shared" si="19"/>
+        <v>145</v>
+      </c>
+      <c r="Y37" s="15">
+        <v>99.4</v>
+      </c>
+      <c r="Z37" s="15">
+        <v>99.9999</v>
+      </c>
+      <c r="AA37" s="13">
+        <v>2e+17</v>
+      </c>
+      <c r="AB37" s="13">
+        <v>2e+17</v>
+      </c>
+    </row>
+    <row r="38" customHeight="1" spans="3:28">
+      <c r="C38" s="1">
+        <v>33</v>
+      </c>
+      <c r="D38" s="1">
+        <f t="shared" si="0"/>
+        <v>3201</v>
+      </c>
+      <c r="E38" s="1">
+        <f t="shared" si="1"/>
+        <v>3300</v>
+      </c>
+      <c r="F38" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="G38" s="14">
+        <v>0.1</v>
+      </c>
+      <c r="H38" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="I38" s="14">
+        <v>10</v>
+      </c>
+      <c r="J38" s="13" t="s">
+        <v>137</v>
+      </c>
+      <c r="K38" s="14">
+        <v>10</v>
+      </c>
+      <c r="L38" s="14" t="s">
+        <v>138</v>
+      </c>
+      <c r="M38" s="14">
+        <v>10</v>
+      </c>
+      <c r="N38" s="14">
+        <v>1000</v>
+      </c>
+      <c r="O38" s="14">
+        <v>0.1</v>
+      </c>
+      <c r="P38" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q38" s="1">
+        <v>0</v>
+      </c>
+      <c r="R38" s="1">
+        <v>0</v>
+      </c>
+      <c r="S38" s="15">
+        <f t="shared" si="15"/>
+        <v>28000</v>
+      </c>
+      <c r="T38" s="15">
+        <f t="shared" si="16"/>
+        <v>28000</v>
+      </c>
+      <c r="U38" s="15">
+        <f t="shared" si="17"/>
+        <v>18000</v>
+      </c>
+      <c r="V38" s="15">
+        <f t="shared" si="18"/>
+        <v>18000</v>
+      </c>
+      <c r="W38" s="15">
+        <f t="shared" si="20"/>
+        <v>205</v>
+      </c>
+      <c r="X38" s="15">
+        <f t="shared" si="19"/>
+        <v>160</v>
+      </c>
+      <c r="Y38" s="15">
+        <v>99.4</v>
+      </c>
+      <c r="Z38" s="15">
+        <v>99.99999</v>
+      </c>
+      <c r="AA38" s="13">
+        <v>2.2e+17</v>
+      </c>
+      <c r="AB38" s="13">
+        <v>2.2e+17</v>
+      </c>
+    </row>
+    <row r="39" customHeight="1" spans="3:28">
+      <c r="C39" s="1">
+        <v>34</v>
+      </c>
+      <c r="D39" s="1">
+        <f t="shared" si="0"/>
+        <v>3301</v>
+      </c>
+      <c r="E39" s="1">
+        <f t="shared" si="1"/>
+        <v>3400</v>
+      </c>
+      <c r="F39" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="G39" s="14">
+        <v>0.1</v>
+      </c>
+      <c r="H39" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="I39" s="14">
+        <v>10</v>
+      </c>
+      <c r="J39" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="K39" s="14">
+        <v>10</v>
+      </c>
+      <c r="L39" s="14" t="s">
+        <v>142</v>
+      </c>
+      <c r="M39" s="14">
+        <v>10</v>
+      </c>
+      <c r="N39" s="14">
+        <v>100000</v>
+      </c>
+      <c r="O39" s="14">
+        <v>1</v>
+      </c>
+      <c r="P39" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q39" s="1">
+        <v>0</v>
+      </c>
+      <c r="R39" s="1">
+        <v>0</v>
+      </c>
+      <c r="S39" s="15">
+        <f t="shared" si="15"/>
+        <v>31000</v>
+      </c>
+      <c r="T39" s="15">
+        <f t="shared" si="16"/>
+        <v>31000</v>
+      </c>
+      <c r="U39" s="15">
+        <f t="shared" si="17"/>
+        <v>20000</v>
+      </c>
+      <c r="V39" s="15">
+        <f t="shared" si="18"/>
+        <v>20000</v>
+      </c>
+      <c r="W39" s="15">
+        <f t="shared" si="20"/>
+        <v>225</v>
+      </c>
+      <c r="X39" s="15">
+        <f t="shared" si="19"/>
+        <v>175</v>
+      </c>
+      <c r="Y39" s="15">
+        <v>99.4</v>
+      </c>
+      <c r="Z39" s="15">
+        <v>99.99999</v>
+      </c>
+      <c r="AA39" s="13">
+        <v>2.4e+17</v>
+      </c>
+      <c r="AB39" s="13">
+        <v>2.4e+17</v>
+      </c>
+    </row>
+    <row r="40" customHeight="1" spans="3:28">
+      <c r="C40" s="1">
+        <v>35</v>
+      </c>
+      <c r="D40" s="1">
+        <f t="shared" si="0"/>
+        <v>3401</v>
+      </c>
+      <c r="E40" s="1">
+        <f t="shared" si="1"/>
+        <v>3500</v>
+      </c>
+      <c r="F40" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="G40" s="14">
+        <v>0.1</v>
+      </c>
+      <c r="H40" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="I40" s="14">
+        <v>10</v>
+      </c>
+      <c r="J40" s="13" t="s">
+        <v>145</v>
+      </c>
+      <c r="K40" s="14">
+        <v>10</v>
+      </c>
+      <c r="L40" s="14" t="s">
+        <v>146</v>
+      </c>
+      <c r="M40" s="14">
+        <v>10</v>
+      </c>
+      <c r="N40" s="14">
+        <v>10000000</v>
+      </c>
+      <c r="O40" s="14">
+        <v>1</v>
+      </c>
+      <c r="P40" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q40" s="1">
+        <v>0</v>
+      </c>
+      <c r="R40" s="1">
+        <v>0</v>
+      </c>
+      <c r="S40" s="15">
+        <f t="shared" si="15"/>
+        <v>34000</v>
+      </c>
+      <c r="T40" s="15">
+        <f t="shared" si="16"/>
+        <v>34000</v>
+      </c>
+      <c r="U40" s="15">
+        <f t="shared" si="17"/>
+        <v>22000</v>
+      </c>
+      <c r="V40" s="15">
+        <f t="shared" si="18"/>
+        <v>22000</v>
+      </c>
+      <c r="W40" s="15">
+        <f t="shared" si="20"/>
+        <v>245</v>
+      </c>
+      <c r="X40" s="15">
+        <f t="shared" si="19"/>
+        <v>190</v>
+      </c>
+      <c r="Y40" s="15">
+        <v>99.4</v>
+      </c>
+      <c r="Z40" s="15">
+        <v>99.99999</v>
+      </c>
+      <c r="AA40" s="13">
+        <v>2.6e+17</v>
+      </c>
+      <c r="AB40" s="13">
+        <v>2.6e+17</v>
+      </c>
+    </row>
+    <row r="41" customHeight="1" spans="3:28">
+      <c r="C41" s="1">
+        <v>36</v>
+      </c>
+      <c r="D41" s="1">
+        <f t="shared" si="0"/>
+        <v>3501</v>
+      </c>
+      <c r="E41" s="1">
+        <f t="shared" si="1"/>
+        <v>3600</v>
+      </c>
+      <c r="F41" s="13" t="s">
+        <v>147</v>
+      </c>
+      <c r="G41" s="14">
+        <v>10</v>
+      </c>
+      <c r="H41" s="13" t="s">
+        <v>148</v>
+      </c>
+      <c r="I41" s="14">
+        <v>100</v>
+      </c>
+      <c r="J41" s="13" t="s">
+        <v>149</v>
+      </c>
+      <c r="K41" s="14">
+        <v>100</v>
+      </c>
+      <c r="L41" s="14" t="s">
+        <v>150</v>
+      </c>
+      <c r="M41" s="14">
+        <v>10</v>
+      </c>
+      <c r="N41" s="14" t="s">
+        <v>151</v>
+      </c>
+      <c r="O41" s="14">
+        <v>1</v>
+      </c>
+      <c r="P41" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q41" s="1">
+        <v>0</v>
+      </c>
+      <c r="R41" s="1">
+        <v>0</v>
+      </c>
+      <c r="S41" s="15">
+        <f t="shared" si="15"/>
+        <v>37000</v>
+      </c>
+      <c r="T41" s="15">
+        <f t="shared" si="16"/>
+        <v>37000</v>
+      </c>
+      <c r="U41" s="15">
+        <f t="shared" si="17"/>
+        <v>24000</v>
+      </c>
+      <c r="V41" s="15">
+        <f t="shared" si="18"/>
+        <v>24000</v>
+      </c>
+      <c r="W41" s="15">
+        <f t="shared" si="20"/>
+        <v>265</v>
+      </c>
+      <c r="X41" s="15">
+        <f t="shared" si="19"/>
+        <v>205</v>
+      </c>
+      <c r="Y41" s="15">
+        <v>99.4</v>
+      </c>
+      <c r="Z41" s="15">
+        <v>99.99999</v>
+      </c>
+      <c r="AA41" s="13">
+        <v>2.8e+17</v>
+      </c>
+      <c r="AB41" s="13">
+        <v>2.8e+17</v>
+      </c>
+    </row>
+    <row r="42" customHeight="1" spans="3:28">
+      <c r="C42" s="1">
+        <v>37</v>
+      </c>
+      <c r="D42" s="1">
+        <f t="shared" si="0"/>
+        <v>3601</v>
+      </c>
+      <c r="E42" s="1">
+        <f t="shared" si="1"/>
+        <v>3700</v>
+      </c>
+      <c r="F42" s="13" t="s">
+        <v>152</v>
+      </c>
+      <c r="G42" s="14">
+        <v>10</v>
+      </c>
+      <c r="H42" s="13" t="s">
+        <v>153</v>
+      </c>
+      <c r="I42" s="14">
+        <v>100</v>
+      </c>
+      <c r="J42" s="13" t="s">
+        <v>154</v>
+      </c>
+      <c r="K42" s="14">
+        <v>100</v>
+      </c>
+      <c r="L42" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="M42" s="14">
+        <v>10</v>
+      </c>
+      <c r="N42" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="O42" s="14">
+        <v>1</v>
+      </c>
+      <c r="P42" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="1">
+        <v>0</v>
+      </c>
+      <c r="R42" s="1">
+        <v>0</v>
+      </c>
+      <c r="S42" s="15">
+        <f t="shared" si="15"/>
+        <v>40000</v>
+      </c>
+      <c r="T42" s="15">
+        <f t="shared" si="16"/>
+        <v>40000</v>
+      </c>
+      <c r="U42" s="15">
+        <f t="shared" si="17"/>
+        <v>26000</v>
+      </c>
+      <c r="V42" s="15">
+        <f t="shared" si="18"/>
+        <v>26000</v>
+      </c>
+      <c r="W42" s="15">
+        <f t="shared" si="20"/>
+        <v>285</v>
+      </c>
+      <c r="X42" s="15">
+        <f t="shared" si="19"/>
+        <v>220</v>
+      </c>
+      <c r="Y42" s="15">
+        <v>99.4</v>
+      </c>
+      <c r="Z42" s="15">
+        <v>99.99999</v>
+      </c>
+      <c r="AA42" s="13">
+        <v>3e+17</v>
+      </c>
+      <c r="AB42" s="13">
+        <v>3e+17</v>
+      </c>
+    </row>
+    <row r="43" customHeight="1" spans="3:28">
+      <c r="C43" s="1">
+        <v>38</v>
+      </c>
+      <c r="D43" s="1">
+        <f t="shared" si="0"/>
+        <v>3701</v>
+      </c>
+      <c r="E43" s="1">
+        <f t="shared" si="1"/>
+        <v>3800</v>
+      </c>
+      <c r="F43" s="13" t="s">
+        <v>156</v>
+      </c>
+      <c r="G43" s="14">
+        <v>10</v>
+      </c>
+      <c r="H43" s="13" t="s">
+        <v>157</v>
+      </c>
+      <c r="I43" s="14">
+        <v>100</v>
+      </c>
+      <c r="J43" s="13" t="s">
+        <v>158</v>
+      </c>
+      <c r="K43" s="14">
+        <v>100</v>
+      </c>
+      <c r="L43" s="14" t="s">
+        <v>159</v>
+      </c>
+      <c r="M43" s="14">
+        <v>10</v>
+      </c>
+      <c r="N43" s="14" t="s">
+        <v>160</v>
+      </c>
+      <c r="O43" s="14">
+        <v>1</v>
+      </c>
+      <c r="P43" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q43" s="1">
+        <v>0</v>
+      </c>
+      <c r="R43" s="1">
+        <v>0</v>
+      </c>
+      <c r="S43" s="15">
+        <f t="shared" si="15"/>
+        <v>43000</v>
+      </c>
+      <c r="T43" s="15">
+        <f t="shared" si="16"/>
+        <v>43000</v>
+      </c>
+      <c r="U43" s="15">
+        <f t="shared" si="17"/>
+        <v>28000</v>
+      </c>
+      <c r="V43" s="15">
+        <f t="shared" si="18"/>
+        <v>28000</v>
+      </c>
+      <c r="W43" s="15">
+        <f t="shared" si="20"/>
+        <v>305</v>
+      </c>
+      <c r="X43" s="15">
+        <f t="shared" si="19"/>
+        <v>235</v>
+      </c>
+      <c r="Y43" s="15">
+        <v>99.4</v>
+      </c>
+      <c r="Z43" s="15">
+        <v>99.99999</v>
+      </c>
+      <c r="AA43" s="13">
+        <v>3.2e+17</v>
+      </c>
+      <c r="AB43" s="13">
+        <v>3.2e+17</v>
+      </c>
+    </row>
+    <row r="44" customHeight="1" spans="3:28">
+      <c r="C44" s="1">
+        <v>39</v>
+      </c>
+      <c r="D44" s="1">
+        <f t="shared" si="0"/>
+        <v>3801</v>
+      </c>
+      <c r="E44" s="1">
+        <f t="shared" si="1"/>
+        <v>3900</v>
+      </c>
+      <c r="F44" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="G44" s="14">
+        <v>10</v>
+      </c>
+      <c r="H44" s="13" t="s">
+        <v>162</v>
+      </c>
+      <c r="I44" s="14">
+        <v>100</v>
+      </c>
+      <c r="J44" s="13" t="s">
+        <v>163</v>
+      </c>
+      <c r="K44" s="14">
+        <v>100</v>
+      </c>
+      <c r="L44" s="14" t="s">
+        <v>164</v>
+      </c>
+      <c r="M44" s="14">
+        <v>10</v>
+      </c>
+      <c r="N44" s="14" t="s">
+        <v>165</v>
+      </c>
+      <c r="O44" s="14">
+        <v>1</v>
+      </c>
+      <c r="P44" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="1">
+        <v>0</v>
+      </c>
+      <c r="R44" s="1">
+        <v>0</v>
+      </c>
+      <c r="S44" s="15">
+        <f t="shared" si="15"/>
+        <v>46000</v>
+      </c>
+      <c r="T44" s="15">
+        <f t="shared" si="16"/>
+        <v>46000</v>
+      </c>
+      <c r="U44" s="15">
+        <f t="shared" si="17"/>
+        <v>30000</v>
+      </c>
+      <c r="V44" s="15">
+        <f t="shared" si="18"/>
+        <v>30000</v>
+      </c>
+      <c r="W44" s="15">
+        <f t="shared" si="20"/>
+        <v>325</v>
+      </c>
+      <c r="X44" s="15">
+        <f t="shared" si="19"/>
+        <v>250</v>
+      </c>
+      <c r="Y44" s="15">
+        <v>99.4</v>
+      </c>
+      <c r="Z44" s="15">
+        <v>99.99999</v>
+      </c>
+      <c r="AA44" s="13">
+        <v>3.4e+17</v>
+      </c>
+      <c r="AB44" s="13">
+        <v>3.4e+17</v>
+      </c>
+    </row>
+    <row r="45" customHeight="1" spans="3:28">
+      <c r="C45" s="1">
+        <v>40</v>
+      </c>
+      <c r="D45" s="1">
+        <f t="shared" si="0"/>
+        <v>3901</v>
+      </c>
+      <c r="E45" s="1">
+        <f t="shared" si="1"/>
+        <v>4000</v>
+      </c>
+      <c r="F45" s="26" t="s">
+        <v>166</v>
+      </c>
+      <c r="G45" s="14">
+        <v>10</v>
+      </c>
+      <c r="H45" s="26" t="s">
+        <v>167</v>
+      </c>
+      <c r="I45" s="14">
+        <v>100</v>
+      </c>
+      <c r="J45" s="26" t="s">
+        <v>168</v>
+      </c>
+      <c r="K45" s="14">
+        <v>100</v>
+      </c>
+      <c r="L45" s="26" t="s">
+        <v>169</v>
+      </c>
+      <c r="M45" s="14">
+        <v>10</v>
+      </c>
+      <c r="N45" s="26" t="s">
+        <v>170</v>
+      </c>
+      <c r="O45" s="14">
+        <v>1</v>
+      </c>
+      <c r="P45" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q45" s="1">
+        <v>0</v>
+      </c>
+      <c r="R45" s="1">
+        <v>0</v>
+      </c>
+      <c r="S45" s="15">
+        <f t="shared" si="15"/>
+        <v>49000</v>
+      </c>
+      <c r="T45" s="15">
+        <f t="shared" si="16"/>
+        <v>49000</v>
+      </c>
+      <c r="U45" s="15">
+        <f t="shared" si="17"/>
+        <v>32000</v>
+      </c>
+      <c r="V45" s="15">
+        <f t="shared" si="18"/>
+        <v>32000</v>
+      </c>
+      <c r="W45" s="15">
+        <f t="shared" si="20"/>
+        <v>345</v>
+      </c>
+      <c r="X45" s="15">
+        <f t="shared" si="19"/>
+        <v>265</v>
+      </c>
+      <c r="Y45" s="15">
+        <v>99.4</v>
+      </c>
+      <c r="Z45" s="15">
+        <v>99.99999</v>
+      </c>
+      <c r="AA45" s="13">
+        <v>3.6e+17</v>
+      </c>
+      <c r="AB45" s="13">
+        <v>3.6e+17</v>
+      </c>
+    </row>
+    <row r="46" customHeight="1" spans="3:28">
+      <c r="C46" s="1">
+        <v>41</v>
+      </c>
+      <c r="D46" s="1">
+        <f t="shared" si="0"/>
+        <v>4001</v>
+      </c>
+      <c r="E46" s="1">
+        <f t="shared" si="1"/>
+        <v>4100</v>
+      </c>
+      <c r="F46" s="26" t="s">
+        <v>171</v>
+      </c>
+      <c r="G46" s="14">
+        <v>10</v>
+      </c>
+      <c r="H46" s="26" t="s">
+        <v>172</v>
+      </c>
+      <c r="I46" s="14">
+        <v>100</v>
+      </c>
+      <c r="J46" s="26" t="s">
+        <v>173</v>
+      </c>
+      <c r="K46" s="14">
+        <v>100</v>
+      </c>
+      <c r="L46" s="26" t="s">
+        <v>174</v>
+      </c>
+      <c r="M46" s="14">
+        <v>10</v>
+      </c>
+      <c r="N46" s="26" t="s">
+        <v>175</v>
+      </c>
+      <c r="O46" s="14">
+        <v>1</v>
+      </c>
+      <c r="P46" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q46" s="1">
+        <v>0</v>
+      </c>
+      <c r="R46" s="1">
+        <v>0</v>
+      </c>
+      <c r="S46" s="15">
+        <f t="shared" si="15"/>
+        <v>52000</v>
+      </c>
+      <c r="T46" s="15">
+        <f t="shared" si="16"/>
+        <v>52000</v>
+      </c>
+      <c r="U46" s="15">
+        <f t="shared" si="17"/>
+        <v>34000</v>
+      </c>
+      <c r="V46" s="15">
+        <f t="shared" si="18"/>
+        <v>34000</v>
+      </c>
+      <c r="W46" s="15">
+        <f t="shared" si="20"/>
+        <v>365</v>
+      </c>
+      <c r="X46" s="15">
+        <f t="shared" si="19"/>
+        <v>280</v>
+      </c>
+      <c r="Y46" s="15">
+        <v>99.4</v>
+      </c>
+      <c r="Z46" s="15">
+        <v>99.99999</v>
+      </c>
+      <c r="AA46" s="13">
+        <v>3.8e+17</v>
+      </c>
+      <c r="AB46" s="13">
+        <v>3.8e+17</v>
+      </c>
+    </row>
+    <row r="47" customHeight="1" spans="3:28">
+      <c r="C47" s="1">
+        <v>42</v>
+      </c>
+      <c r="D47" s="1">
+        <f t="shared" si="0"/>
+        <v>4101</v>
+      </c>
+      <c r="E47" s="1">
+        <f t="shared" si="1"/>
+        <v>4200</v>
+      </c>
+      <c r="F47" s="26" t="s">
+        <v>176</v>
+      </c>
+      <c r="G47" s="14">
+        <v>10</v>
+      </c>
+      <c r="H47" s="26" t="s">
+        <v>177</v>
+      </c>
+      <c r="I47" s="14">
+        <v>100</v>
+      </c>
+      <c r="J47" s="26" t="s">
+        <v>178</v>
+      </c>
+      <c r="K47" s="14">
+        <v>100</v>
+      </c>
+      <c r="L47" s="26" t="s">
+        <v>179</v>
+      </c>
+      <c r="M47" s="14">
+        <v>10</v>
+      </c>
+      <c r="N47" s="26" t="s">
+        <v>180</v>
+      </c>
+      <c r="O47" s="14">
+        <v>1</v>
+      </c>
+      <c r="P47" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="1">
+        <v>0</v>
+      </c>
+      <c r="R47" s="1">
+        <v>0</v>
+      </c>
+      <c r="S47" s="15">
+        <f t="shared" si="15"/>
+        <v>55000</v>
+      </c>
+      <c r="T47" s="15">
+        <f t="shared" si="16"/>
+        <v>55000</v>
+      </c>
+      <c r="U47" s="15">
+        <f t="shared" si="17"/>
+        <v>36000</v>
+      </c>
+      <c r="V47" s="15">
+        <f t="shared" si="18"/>
+        <v>36000</v>
+      </c>
+      <c r="W47" s="15">
+        <f t="shared" si="20"/>
+        <v>385</v>
+      </c>
+      <c r="X47" s="15">
+        <f t="shared" si="19"/>
+        <v>295</v>
+      </c>
+      <c r="Y47" s="15">
+        <v>99.4</v>
+      </c>
+      <c r="Z47" s="15">
+        <v>99.99999</v>
+      </c>
+      <c r="AA47" s="13">
+        <v>4e+17</v>
+      </c>
+      <c r="AB47" s="13">
+        <v>4e+17</v>
+      </c>
+    </row>
+    <row r="48" customHeight="1" spans="3:28">
+      <c r="C48" s="1">
+        <v>43</v>
+      </c>
+      <c r="D48" s="1">
+        <f t="shared" si="0"/>
+        <v>4201</v>
+      </c>
+      <c r="E48" s="1">
+        <f t="shared" si="1"/>
+        <v>4300</v>
+      </c>
+      <c r="F48" s="26" t="s">
+        <v>181</v>
+      </c>
+      <c r="G48" s="14">
+        <v>10</v>
+      </c>
+      <c r="H48" s="26" t="s">
+        <v>182</v>
+      </c>
+      <c r="I48" s="14">
+        <v>100</v>
+      </c>
+      <c r="J48" s="26" t="s">
+        <v>183</v>
+      </c>
+      <c r="K48" s="14">
+        <v>100</v>
+      </c>
+      <c r="L48" s="26" t="s">
+        <v>184</v>
+      </c>
+      <c r="M48" s="14">
+        <v>10</v>
+      </c>
+      <c r="N48" s="26" t="s">
+        <v>185</v>
+      </c>
+      <c r="O48" s="14">
+        <v>1</v>
+      </c>
+      <c r="P48" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q48" s="1">
+        <v>0</v>
+      </c>
+      <c r="R48" s="1">
+        <v>0</v>
+      </c>
+      <c r="S48" s="15">
+        <f t="shared" si="15"/>
+        <v>58000</v>
+      </c>
+      <c r="T48" s="15">
+        <f t="shared" si="16"/>
+        <v>58000</v>
+      </c>
+      <c r="U48" s="15">
+        <f t="shared" si="17"/>
+        <v>38000</v>
+      </c>
+      <c r="V48" s="15">
+        <f t="shared" si="18"/>
+        <v>38000</v>
+      </c>
+      <c r="W48" s="15">
+        <f t="shared" si="20"/>
+        <v>405</v>
+      </c>
+      <c r="X48" s="15">
+        <f t="shared" si="19"/>
+        <v>310</v>
+      </c>
+      <c r="Y48" s="15">
+        <v>99.4</v>
+      </c>
+      <c r="Z48" s="15">
+        <v>99.99999</v>
+      </c>
+      <c r="AA48" s="13">
+        <v>4.2e+17</v>
+      </c>
+      <c r="AB48" s="13">
+        <v>4.2e+17</v>
+      </c>
+    </row>
+    <row r="49" customHeight="1" spans="3:28">
+      <c r="C49" s="1">
+        <v>44</v>
+      </c>
+      <c r="D49" s="1">
+        <f t="shared" si="0"/>
+        <v>4301</v>
+      </c>
+      <c r="E49" s="1">
+        <f t="shared" si="1"/>
+        <v>4400</v>
+      </c>
+      <c r="F49" s="26" t="s">
+        <v>186</v>
+      </c>
+      <c r="G49" s="14">
+        <v>10</v>
+      </c>
+      <c r="H49" s="26" t="s">
+        <v>187</v>
+      </c>
+      <c r="I49" s="14">
+        <v>100</v>
+      </c>
+      <c r="J49" s="26" t="s">
+        <v>188</v>
+      </c>
+      <c r="K49" s="14">
+        <v>100</v>
+      </c>
+      <c r="L49" s="26" t="s">
+        <v>189</v>
+      </c>
+      <c r="M49" s="14">
+        <v>10</v>
+      </c>
+      <c r="N49" s="26" t="s">
+        <v>190</v>
+      </c>
+      <c r="O49" s="14">
+        <v>1</v>
+      </c>
+      <c r="P49" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q49" s="1">
+        <v>0</v>
+      </c>
+      <c r="R49" s="1">
+        <v>0</v>
+      </c>
+      <c r="S49" s="15">
+        <f t="shared" si="15"/>
+        <v>61000</v>
+      </c>
+      <c r="T49" s="15">
+        <f t="shared" si="16"/>
+        <v>61000</v>
+      </c>
+      <c r="U49" s="15">
+        <f t="shared" si="17"/>
+        <v>40000</v>
+      </c>
+      <c r="V49" s="15">
+        <f t="shared" si="18"/>
+        <v>40000</v>
+      </c>
+      <c r="W49" s="15">
+        <f t="shared" si="20"/>
+        <v>425</v>
+      </c>
+      <c r="X49" s="15">
+        <f t="shared" si="19"/>
+        <v>325</v>
+      </c>
+      <c r="Y49" s="15">
+        <v>99.4</v>
+      </c>
+      <c r="Z49" s="15">
+        <v>99.99999</v>
+      </c>
+      <c r="AA49" s="13">
+        <v>4.4e+17</v>
+      </c>
+      <c r="AB49" s="13">
+        <v>4.4e+17</v>
+      </c>
+    </row>
+    <row r="50" customHeight="1" spans="3:28">
+      <c r="C50" s="1">
+        <v>45</v>
+      </c>
+      <c r="D50" s="1">
+        <f t="shared" si="0"/>
+        <v>4401</v>
+      </c>
+      <c r="E50" s="1">
+        <f t="shared" si="1"/>
+        <v>4500</v>
+      </c>
+      <c r="F50" s="26" t="s">
+        <v>191</v>
+      </c>
+      <c r="G50" s="14">
+        <v>10</v>
+      </c>
+      <c r="H50" s="26" t="s">
+        <v>192</v>
+      </c>
+      <c r="I50" s="14">
+        <v>100</v>
+      </c>
+      <c r="J50" s="26" t="s">
+        <v>193</v>
+      </c>
+      <c r="K50" s="14">
+        <v>100</v>
+      </c>
+      <c r="L50" s="26" t="s">
+        <v>194</v>
+      </c>
+      <c r="M50" s="14">
+        <v>10</v>
+      </c>
+      <c r="N50" s="26" t="s">
+        <v>195</v>
+      </c>
+      <c r="O50" s="14">
+        <v>1</v>
+      </c>
+      <c r="P50" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="1">
+        <v>0</v>
+      </c>
+      <c r="R50" s="1">
+        <v>0</v>
+      </c>
+      <c r="S50" s="15">
+        <f t="shared" si="15"/>
+        <v>64000</v>
+      </c>
+      <c r="T50" s="15">
+        <f t="shared" si="16"/>
+        <v>64000</v>
+      </c>
+      <c r="U50" s="15">
+        <f t="shared" si="17"/>
+        <v>42000</v>
+      </c>
+      <c r="V50" s="15">
+        <f t="shared" si="18"/>
+        <v>42000</v>
+      </c>
+      <c r="W50" s="15">
+        <f t="shared" si="20"/>
+        <v>445</v>
+      </c>
+      <c r="X50" s="15">
+        <f t="shared" si="19"/>
+        <v>340</v>
+      </c>
+      <c r="Y50" s="15">
+        <v>99.4</v>
+      </c>
+      <c r="Z50" s="15">
+        <v>99.99999</v>
+      </c>
+      <c r="AA50" s="13">
+        <v>4.6e+17</v>
+      </c>
+      <c r="AB50" s="13">
+        <v>4.6e+17</v>
+      </c>
+    </row>
+    <row r="51" s="3" customFormat="1" customHeight="1" spans="3:28">
+      <c r="C51" s="19">
+        <v>46</v>
+      </c>
+      <c r="D51" s="19">
+        <f t="shared" si="0"/>
+        <v>4501</v>
+      </c>
+      <c r="E51" s="19">
+        <f t="shared" si="1"/>
+        <v>4600</v>
+      </c>
+      <c r="F51" s="27" t="s">
+        <v>196</v>
+      </c>
+      <c r="G51" s="21">
+        <v>100</v>
+      </c>
+      <c r="H51" s="27" t="s">
+        <v>197</v>
+      </c>
+      <c r="I51" s="21">
+        <v>100</v>
+      </c>
+      <c r="J51" s="27" t="s">
+        <v>198</v>
+      </c>
+      <c r="K51" s="21">
+        <v>100</v>
+      </c>
+      <c r="L51" s="27" t="s">
+        <v>199</v>
+      </c>
+      <c r="M51" s="21">
+        <v>100</v>
+      </c>
+      <c r="N51" s="27" t="s">
+        <v>200</v>
+      </c>
+      <c r="O51" s="21">
+        <v>10</v>
+      </c>
+      <c r="P51" s="1">
+        <v>10</v>
+      </c>
+      <c r="Q51" s="1">
+        <v>0</v>
+      </c>
+      <c r="R51" s="1">
+        <v>100</v>
+      </c>
+      <c r="S51" s="3">
+        <f t="shared" si="15"/>
+        <v>67000</v>
+      </c>
+      <c r="T51" s="3">
+        <f t="shared" si="16"/>
+        <v>67000</v>
+      </c>
+      <c r="U51" s="3">
+        <f t="shared" si="17"/>
+        <v>44000</v>
+      </c>
+      <c r="V51" s="3">
+        <f t="shared" si="18"/>
+        <v>44000</v>
+      </c>
+      <c r="W51" s="3">
+        <f t="shared" si="20"/>
+        <v>465</v>
+      </c>
+      <c r="X51" s="3">
+        <f t="shared" si="19"/>
+        <v>355</v>
+      </c>
+      <c r="Y51" s="3">
+        <v>99.4</v>
+      </c>
+      <c r="Z51" s="3">
+        <v>99.99999</v>
+      </c>
+      <c r="AA51" s="20">
+        <v>5e+17</v>
+      </c>
+      <c r="AB51" s="20">
+        <v>5e+17</v>
+      </c>
+    </row>
+    <row r="52" customHeight="1" spans="3:28">
+      <c r="C52" s="1">
+        <v>47</v>
+      </c>
+      <c r="D52" s="1">
+        <f t="shared" si="0"/>
+        <v>4601</v>
+      </c>
+      <c r="E52" s="1">
+        <f t="shared" si="1"/>
+        <v>4700</v>
+      </c>
+      <c r="F52" s="26" t="s">
+        <v>201</v>
+      </c>
+      <c r="G52" s="14">
+        <v>100</v>
+      </c>
+      <c r="H52" s="26" t="s">
+        <v>202</v>
+      </c>
+      <c r="I52" s="14">
+        <v>100</v>
+      </c>
+      <c r="J52" s="26" t="s">
+        <v>203</v>
+      </c>
+      <c r="K52" s="14">
+        <v>100</v>
+      </c>
+      <c r="L52" s="26" t="s">
+        <v>204</v>
+      </c>
+      <c r="M52" s="14">
+        <v>100</v>
+      </c>
+      <c r="N52" s="26" t="s">
+        <v>205</v>
+      </c>
+      <c r="O52" s="14">
+        <v>100</v>
+      </c>
+      <c r="P52" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q52" s="1">
+        <v>0</v>
+      </c>
+      <c r="R52" s="1">
+        <v>100</v>
+      </c>
+      <c r="S52" s="15">
+        <f t="shared" si="15"/>
+        <v>70000</v>
+      </c>
+      <c r="T52" s="15">
+        <f t="shared" si="16"/>
+        <v>70000</v>
+      </c>
+      <c r="U52" s="15">
+        <f t="shared" si="17"/>
+        <v>46000</v>
+      </c>
+      <c r="V52" s="15">
+        <f t="shared" si="18"/>
+        <v>46000</v>
+      </c>
+      <c r="W52" s="15">
+        <f t="shared" si="20"/>
+        <v>485</v>
+      </c>
+      <c r="X52" s="15">
+        <f t="shared" si="19"/>
+        <v>370</v>
+      </c>
+      <c r="Y52" s="15">
+        <v>99.4</v>
+      </c>
+      <c r="Z52" s="15">
+        <v>99.99999</v>
+      </c>
+      <c r="AA52" s="13">
+        <v>5.4e+17</v>
+      </c>
+      <c r="AB52" s="13">
+        <v>5.4e+17</v>
+      </c>
+    </row>
+    <row r="53" customHeight="1" spans="3:28">
+      <c r="C53" s="1">
         <v>48</v>
       </c>
-      <c r="G15" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="H15" s="11" t="s">
+      <c r="D53" s="1">
+        <f t="shared" si="0"/>
+        <v>4701</v>
+      </c>
+      <c r="E53" s="1">
+        <f t="shared" si="1"/>
+        <v>4800</v>
+      </c>
+      <c r="F53" s="26" t="s">
+        <v>206</v>
+      </c>
+      <c r="G53" s="14">
+        <v>100</v>
+      </c>
+      <c r="H53" s="26" t="s">
+        <v>207</v>
+      </c>
+      <c r="I53" s="14">
+        <v>100</v>
+      </c>
+      <c r="J53" s="26" t="s">
+        <v>208</v>
+      </c>
+      <c r="K53" s="14">
+        <v>100</v>
+      </c>
+      <c r="L53" s="26" t="s">
+        <v>209</v>
+      </c>
+      <c r="M53" s="14">
+        <v>100</v>
+      </c>
+      <c r="N53" s="26" t="s">
+        <v>210</v>
+      </c>
+      <c r="O53" s="14">
+        <v>100</v>
+      </c>
+      <c r="P53" s="1">
+        <v>1000</v>
+      </c>
+      <c r="Q53" s="1">
+        <v>0</v>
+      </c>
+      <c r="R53" s="1">
+        <v>100</v>
+      </c>
+      <c r="S53" s="15">
+        <f t="shared" si="15"/>
+        <v>73000</v>
+      </c>
+      <c r="T53" s="15">
+        <f t="shared" si="16"/>
+        <v>73000</v>
+      </c>
+      <c r="U53" s="15">
+        <f t="shared" si="17"/>
+        <v>48000</v>
+      </c>
+      <c r="V53" s="15">
+        <f t="shared" si="18"/>
+        <v>48000</v>
+      </c>
+      <c r="W53" s="15">
+        <f t="shared" si="20"/>
+        <v>505</v>
+      </c>
+      <c r="X53" s="15">
+        <f t="shared" si="19"/>
+        <v>385</v>
+      </c>
+      <c r="Y53" s="15">
+        <v>99.4</v>
+      </c>
+      <c r="Z53" s="15">
+        <v>99.99999</v>
+      </c>
+      <c r="AA53" s="13">
+        <v>5.8e+17</v>
+      </c>
+      <c r="AB53" s="13">
+        <v>5.8e+17</v>
+      </c>
+    </row>
+    <row r="54" customHeight="1" spans="3:28">
+      <c r="C54" s="1">
         <v>49</v>
       </c>
-      <c r="I15" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="J15" s="11" t="s">
+      <c r="D54" s="1">
+        <f t="shared" si="0"/>
+        <v>4801</v>
+      </c>
+      <c r="E54" s="1">
+        <f t="shared" si="1"/>
+        <v>4900</v>
+      </c>
+      <c r="F54" s="26" t="s">
+        <v>211</v>
+      </c>
+      <c r="G54" s="14">
+        <v>100</v>
+      </c>
+      <c r="H54" s="26" t="s">
+        <v>188</v>
+      </c>
+      <c r="I54" s="14">
+        <v>100</v>
+      </c>
+      <c r="J54" s="26" t="s">
+        <v>212</v>
+      </c>
+      <c r="K54" s="14">
+        <v>100</v>
+      </c>
+      <c r="L54" s="26" t="s">
+        <v>186</v>
+      </c>
+      <c r="M54" s="14">
+        <v>100</v>
+      </c>
+      <c r="N54" s="26" t="s">
+        <v>213</v>
+      </c>
+      <c r="O54" s="14">
+        <v>100</v>
+      </c>
+      <c r="P54" s="28" t="s">
+        <v>214</v>
+      </c>
+      <c r="Q54" s="1">
+        <v>0</v>
+      </c>
+      <c r="R54" s="1">
+        <v>100</v>
+      </c>
+      <c r="S54" s="15">
+        <f t="shared" si="15"/>
+        <v>76000</v>
+      </c>
+      <c r="T54" s="15">
+        <f t="shared" si="16"/>
+        <v>76000</v>
+      </c>
+      <c r="U54" s="15">
+        <f t="shared" si="17"/>
+        <v>50000</v>
+      </c>
+      <c r="V54" s="15">
+        <f t="shared" si="18"/>
+        <v>50000</v>
+      </c>
+      <c r="W54" s="15">
+        <f t="shared" si="20"/>
+        <v>525</v>
+      </c>
+      <c r="X54" s="15">
+        <f t="shared" si="19"/>
+        <v>400</v>
+      </c>
+      <c r="Y54" s="15">
+        <v>99.4</v>
+      </c>
+      <c r="Z54" s="15">
+        <v>99.99999</v>
+      </c>
+      <c r="AA54" s="13">
+        <v>6.2e+17</v>
+      </c>
+      <c r="AB54" s="13">
+        <v>6.2e+17</v>
+      </c>
+    </row>
+    <row r="55" customHeight="1" spans="3:28">
+      <c r="C55" s="1">
         <v>50</v>
       </c>
-      <c r="K15" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="L15" s="9">
-        <v>1000</v>
-      </c>
-      <c r="M15" s="9">
-        <v>1000</v>
-      </c>
-      <c r="N15" s="9">
-        <v>1000</v>
-      </c>
-      <c r="O15" s="9">
-        <v>1000</v>
-      </c>
-      <c r="P15" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="9">
-        <v>99</v>
-      </c>
-      <c r="R15" s="8">
-        <v>1000000000000</v>
-      </c>
-      <c r="S15" s="8">
-        <v>1000000000000</v>
-      </c>
-    </row>
-    <row r="23" customHeight="1" spans="6:6">
-      <c r="F23" s="8"/>
-    </row>
-    <row r="24" customHeight="1" spans="6:6">
-      <c r="F24" s="8"/>
-    </row>
-    <row r="27" customHeight="1" spans="8:9">
-      <c r="H27" s="8"/>
-      <c r="I27" s="8"/>
-    </row>
-    <row r="28" customHeight="1" spans="8:9">
-      <c r="H28" s="8"/>
-      <c r="I28" s="8"/>
-    </row>
-    <row r="29" customHeight="1" spans="8:9">
-      <c r="H29" s="8"/>
-      <c r="I29" s="8"/>
-    </row>
-    <row r="30" customHeight="1" spans="8:9">
-      <c r="H30" s="8"/>
-      <c r="I30" s="8"/>
-    </row>
-    <row r="31" customHeight="1" spans="8:9">
-      <c r="H31" s="8"/>
-      <c r="I31" s="8"/>
-    </row>
-    <row r="32" customHeight="1" spans="8:9">
-      <c r="H32" s="8"/>
-      <c r="I32" s="8"/>
-    </row>
-    <row r="33" customHeight="1" spans="8:9">
-      <c r="H33" s="8"/>
-      <c r="I33" s="8"/>
-    </row>
-    <row r="34" customHeight="1" spans="8:9">
-      <c r="H34" s="8"/>
-      <c r="I34" s="8"/>
-    </row>
-    <row r="35" customHeight="1" spans="8:9">
-      <c r="H35" s="8"/>
-      <c r="I35" s="8"/>
-    </row>
-    <row r="36" customHeight="1" spans="8:9">
-      <c r="H36" s="8"/>
-      <c r="I36" s="8"/>
+      <c r="D55" s="1">
+        <f t="shared" si="0"/>
+        <v>4901</v>
+      </c>
+      <c r="E55" s="1">
+        <f t="shared" si="1"/>
+        <v>5000</v>
+      </c>
+      <c r="F55" s="26" t="s">
+        <v>215</v>
+      </c>
+      <c r="G55" s="14">
+        <v>100</v>
+      </c>
+      <c r="H55" s="26" t="s">
+        <v>216</v>
+      </c>
+      <c r="I55" s="14">
+        <v>100</v>
+      </c>
+      <c r="J55" s="26" t="s">
+        <v>217</v>
+      </c>
+      <c r="K55" s="14">
+        <v>100</v>
+      </c>
+      <c r="L55" s="26" t="s">
+        <v>218</v>
+      </c>
+      <c r="M55" s="14">
+        <v>100</v>
+      </c>
+      <c r="N55" s="26" t="s">
+        <v>219</v>
+      </c>
+      <c r="O55" s="14">
+        <v>100</v>
+      </c>
+      <c r="P55" s="28" t="s">
+        <v>220</v>
+      </c>
+      <c r="Q55" s="1">
+        <v>0</v>
+      </c>
+      <c r="R55" s="1">
+        <v>100</v>
+      </c>
+      <c r="S55" s="15">
+        <f t="shared" si="15"/>
+        <v>79000</v>
+      </c>
+      <c r="T55" s="15">
+        <f t="shared" si="16"/>
+        <v>79000</v>
+      </c>
+      <c r="U55" s="15">
+        <f t="shared" si="17"/>
+        <v>52000</v>
+      </c>
+      <c r="V55" s="15">
+        <f t="shared" si="18"/>
+        <v>52000</v>
+      </c>
+      <c r="W55" s="15">
+        <f t="shared" si="20"/>
+        <v>545</v>
+      </c>
+      <c r="X55" s="15">
+        <f t="shared" si="19"/>
+        <v>415</v>
+      </c>
+      <c r="Y55" s="15">
+        <v>99.4</v>
+      </c>
+      <c r="Z55" s="15">
+        <v>99.99999</v>
+      </c>
+      <c r="AA55" s="13">
+        <v>6.4e+17</v>
+      </c>
+      <c r="AB55" s="13">
+        <v>6.4e+17</v>
+      </c>
+    </row>
+    <row r="56" customHeight="1" spans="3:28">
+      <c r="C56" s="1">
+        <v>51</v>
+      </c>
+      <c r="D56" s="1">
+        <f t="shared" si="0"/>
+        <v>5001</v>
+      </c>
+      <c r="E56" s="1">
+        <f t="shared" si="1"/>
+        <v>5100</v>
+      </c>
+      <c r="F56" s="26" t="s">
+        <v>187</v>
+      </c>
+      <c r="G56" s="14">
+        <v>100</v>
+      </c>
+      <c r="H56" s="26" t="s">
+        <v>221</v>
+      </c>
+      <c r="I56" s="14">
+        <v>100</v>
+      </c>
+      <c r="J56" s="26" t="s">
+        <v>222</v>
+      </c>
+      <c r="K56" s="14">
+        <v>100</v>
+      </c>
+      <c r="L56" s="26" t="s">
+        <v>196</v>
+      </c>
+      <c r="M56" s="14">
+        <v>100</v>
+      </c>
+      <c r="N56" s="26" t="s">
+        <v>223</v>
+      </c>
+      <c r="O56" s="14">
+        <v>1</v>
+      </c>
+      <c r="P56" s="28" t="s">
+        <v>224</v>
+      </c>
+      <c r="Q56" s="1">
+        <v>10</v>
+      </c>
+      <c r="R56" s="1">
+        <v>150</v>
+      </c>
+      <c r="S56" s="15">
+        <f t="shared" si="15"/>
+        <v>82000</v>
+      </c>
+      <c r="T56" s="15">
+        <f t="shared" si="16"/>
+        <v>82000</v>
+      </c>
+      <c r="U56" s="15">
+        <f t="shared" si="17"/>
+        <v>54000</v>
+      </c>
+      <c r="V56" s="15">
+        <f t="shared" si="18"/>
+        <v>54000</v>
+      </c>
+      <c r="W56" s="15">
+        <f t="shared" si="20"/>
+        <v>565</v>
+      </c>
+      <c r="X56" s="15">
+        <f t="shared" si="19"/>
+        <v>430</v>
+      </c>
+      <c r="Y56" s="15">
+        <v>99.4</v>
+      </c>
+      <c r="Z56" s="15">
+        <v>99.99999</v>
+      </c>
+      <c r="AA56" s="13">
+        <v>6.4e+17</v>
+      </c>
+      <c r="AB56" s="13">
+        <v>6.4e+17</v>
+      </c>
+    </row>
+    <row r="57" customHeight="1" spans="3:28">
+      <c r="C57" s="1">
+        <v>52</v>
+      </c>
+      <c r="D57" s="1">
+        <f t="shared" si="0"/>
+        <v>5101</v>
+      </c>
+      <c r="E57" s="1">
+        <f t="shared" si="1"/>
+        <v>5200</v>
+      </c>
+      <c r="F57" s="26" t="s">
+        <v>192</v>
+      </c>
+      <c r="G57" s="14">
+        <v>100</v>
+      </c>
+      <c r="H57" s="26" t="s">
+        <v>225</v>
+      </c>
+      <c r="I57" s="14">
+        <v>100</v>
+      </c>
+      <c r="J57" s="26" t="s">
+        <v>226</v>
+      </c>
+      <c r="K57" s="14">
+        <v>100</v>
+      </c>
+      <c r="L57" s="26" t="s">
+        <v>201</v>
+      </c>
+      <c r="M57" s="14">
+        <v>100</v>
+      </c>
+      <c r="N57" s="26" t="s">
+        <v>227</v>
+      </c>
+      <c r="O57" s="14">
+        <v>1</v>
+      </c>
+      <c r="P57" s="28" t="s">
+        <v>228</v>
+      </c>
+      <c r="Q57" s="1">
+        <v>10</v>
+      </c>
+      <c r="R57" s="1">
+        <v>150</v>
+      </c>
+      <c r="S57" s="15">
+        <f t="shared" si="15"/>
+        <v>85000</v>
+      </c>
+      <c r="T57" s="15">
+        <f t="shared" si="16"/>
+        <v>85000</v>
+      </c>
+      <c r="U57" s="15">
+        <f t="shared" si="17"/>
+        <v>56000</v>
+      </c>
+      <c r="V57" s="15">
+        <f t="shared" si="18"/>
+        <v>56000</v>
+      </c>
+      <c r="W57" s="15">
+        <f t="shared" si="20"/>
+        <v>585</v>
+      </c>
+      <c r="X57" s="15">
+        <f t="shared" si="19"/>
+        <v>445</v>
+      </c>
+      <c r="Y57" s="15">
+        <v>99.4</v>
+      </c>
+      <c r="Z57" s="15">
+        <v>99.99999</v>
+      </c>
+      <c r="AA57" s="13">
+        <v>6.6e+17</v>
+      </c>
+      <c r="AB57" s="13">
+        <v>6.6e+17</v>
+      </c>
+    </row>
+    <row r="58" customHeight="1" spans="3:28">
+      <c r="C58" s="1">
+        <v>53</v>
+      </c>
+      <c r="D58" s="1">
+        <f t="shared" si="0"/>
+        <v>5201</v>
+      </c>
+      <c r="E58" s="1">
+        <f t="shared" si="1"/>
+        <v>5300</v>
+      </c>
+      <c r="F58" s="26" t="s">
+        <v>197</v>
+      </c>
+      <c r="G58" s="14">
+        <v>100</v>
+      </c>
+      <c r="H58" s="26" t="s">
+        <v>229</v>
+      </c>
+      <c r="I58" s="14">
+        <v>100</v>
+      </c>
+      <c r="J58" s="26" t="s">
+        <v>230</v>
+      </c>
+      <c r="K58" s="14">
+        <v>100</v>
+      </c>
+      <c r="L58" s="26" t="s">
+        <v>206</v>
+      </c>
+      <c r="M58" s="14">
+        <v>100</v>
+      </c>
+      <c r="N58" s="26" t="s">
+        <v>174</v>
+      </c>
+      <c r="O58" s="14">
+        <v>1</v>
+      </c>
+      <c r="P58" s="28" t="s">
+        <v>231</v>
+      </c>
+      <c r="Q58" s="1">
+        <v>10</v>
+      </c>
+      <c r="R58" s="1">
+        <v>150</v>
+      </c>
+      <c r="S58" s="15">
+        <f t="shared" si="15"/>
+        <v>88000</v>
+      </c>
+      <c r="T58" s="15">
+        <f t="shared" si="16"/>
+        <v>88000</v>
+      </c>
+      <c r="U58" s="15">
+        <f t="shared" si="17"/>
+        <v>58000</v>
+      </c>
+      <c r="V58" s="15">
+        <f t="shared" si="18"/>
+        <v>58000</v>
+      </c>
+      <c r="W58" s="15">
+        <f t="shared" si="20"/>
+        <v>605</v>
+      </c>
+      <c r="X58" s="15">
+        <f t="shared" si="19"/>
+        <v>460</v>
+      </c>
+      <c r="Y58" s="15">
+        <v>99.4</v>
+      </c>
+      <c r="Z58" s="15">
+        <v>99.99999</v>
+      </c>
+      <c r="AA58" s="13">
+        <v>6.8e+17</v>
+      </c>
+      <c r="AB58" s="13">
+        <v>6.8e+17</v>
+      </c>
+    </row>
+    <row r="59" customHeight="1" spans="3:28">
+      <c r="C59" s="1">
+        <v>54</v>
+      </c>
+      <c r="D59" s="1">
+        <f t="shared" si="0"/>
+        <v>5301</v>
+      </c>
+      <c r="E59" s="1">
+        <f t="shared" si="1"/>
+        <v>5400</v>
+      </c>
+      <c r="F59" s="26" t="s">
+        <v>202</v>
+      </c>
+      <c r="G59" s="14">
+        <v>100</v>
+      </c>
+      <c r="H59" s="26" t="s">
+        <v>232</v>
+      </c>
+      <c r="I59" s="14">
+        <v>100</v>
+      </c>
+      <c r="J59" s="26" t="s">
+        <v>233</v>
+      </c>
+      <c r="K59" s="14">
+        <v>100</v>
+      </c>
+      <c r="L59" s="26" t="s">
+        <v>211</v>
+      </c>
+      <c r="M59" s="14">
+        <v>100</v>
+      </c>
+      <c r="N59" s="26" t="s">
+        <v>234</v>
+      </c>
+      <c r="O59" s="14">
+        <v>1</v>
+      </c>
+      <c r="P59" s="28" t="s">
+        <v>170</v>
+      </c>
+      <c r="Q59" s="1">
+        <v>10</v>
+      </c>
+      <c r="R59" s="1">
+        <v>150</v>
+      </c>
+      <c r="S59" s="15">
+        <f t="shared" si="15"/>
+        <v>91000</v>
+      </c>
+      <c r="T59" s="15">
+        <f t="shared" si="16"/>
+        <v>91000</v>
+      </c>
+      <c r="U59" s="15">
+        <f t="shared" si="17"/>
+        <v>60000</v>
+      </c>
+      <c r="V59" s="15">
+        <f t="shared" si="18"/>
+        <v>60000</v>
+      </c>
+      <c r="W59" s="15">
+        <f t="shared" si="20"/>
+        <v>625</v>
+      </c>
+      <c r="X59" s="15">
+        <f t="shared" si="19"/>
+        <v>475</v>
+      </c>
+      <c r="Y59" s="15">
+        <v>99.4</v>
+      </c>
+      <c r="Z59" s="15">
+        <v>99.99999</v>
+      </c>
+      <c r="AA59" s="13">
+        <v>7e+17</v>
+      </c>
+      <c r="AB59" s="13">
+        <v>7e+17</v>
+      </c>
+    </row>
+    <row r="60" customHeight="1" spans="3:28">
+      <c r="C60" s="1">
+        <v>55</v>
+      </c>
+      <c r="D60" s="1">
+        <f t="shared" si="0"/>
+        <v>5401</v>
+      </c>
+      <c r="E60" s="1">
+        <f t="shared" si="1"/>
+        <v>5500</v>
+      </c>
+      <c r="F60" s="26" t="s">
+        <v>207</v>
+      </c>
+      <c r="G60" s="14">
+        <v>100</v>
+      </c>
+      <c r="H60" s="26" t="s">
+        <v>235</v>
+      </c>
+      <c r="I60" s="14">
+        <v>100</v>
+      </c>
+      <c r="J60" s="26" t="s">
+        <v>236</v>
+      </c>
+      <c r="K60" s="14">
+        <v>100</v>
+      </c>
+      <c r="L60" s="26" t="s">
+        <v>215</v>
+      </c>
+      <c r="M60" s="14">
+        <v>100</v>
+      </c>
+      <c r="N60" s="26" t="s">
+        <v>237</v>
+      </c>
+      <c r="O60" s="14">
+        <v>1</v>
+      </c>
+      <c r="P60" s="28" t="s">
+        <v>238</v>
+      </c>
+      <c r="Q60" s="1">
+        <v>10</v>
+      </c>
+      <c r="R60" s="1">
+        <v>150</v>
+      </c>
+      <c r="S60" s="15">
+        <f t="shared" si="15"/>
+        <v>94000</v>
+      </c>
+      <c r="T60" s="15">
+        <f t="shared" si="16"/>
+        <v>94000</v>
+      </c>
+      <c r="U60" s="15">
+        <f t="shared" si="17"/>
+        <v>62000</v>
+      </c>
+      <c r="V60" s="15">
+        <f t="shared" si="18"/>
+        <v>62000</v>
+      </c>
+      <c r="W60" s="15">
+        <f t="shared" si="20"/>
+        <v>645</v>
+      </c>
+      <c r="X60" s="15">
+        <f t="shared" si="19"/>
+        <v>490</v>
+      </c>
+      <c r="Y60" s="15">
+        <v>99.4</v>
+      </c>
+      <c r="Z60" s="15">
+        <v>99.99999</v>
+      </c>
+      <c r="AA60" s="13">
+        <v>7.2e+17</v>
+      </c>
+      <c r="AB60" s="13">
+        <v>7.2e+17</v>
+      </c>
+    </row>
+    <row r="61" s="4" customFormat="1" customHeight="1" spans="3:28">
+      <c r="C61" s="22">
+        <v>56</v>
+      </c>
+      <c r="D61" s="22">
+        <f t="shared" si="0"/>
+        <v>5501</v>
+      </c>
+      <c r="E61" s="22">
+        <f t="shared" si="1"/>
+        <v>5600</v>
+      </c>
+      <c r="F61" s="29" t="s">
+        <v>188</v>
+      </c>
+      <c r="G61" s="24">
+        <v>100</v>
+      </c>
+      <c r="H61" s="29" t="s">
+        <v>239</v>
+      </c>
+      <c r="I61" s="24">
+        <v>0</v>
+      </c>
+      <c r="J61" s="29" t="s">
+        <v>240</v>
+      </c>
+      <c r="K61" s="24">
+        <v>100</v>
+      </c>
+      <c r="L61" s="29" t="s">
+        <v>187</v>
+      </c>
+      <c r="M61" s="24">
+        <v>100</v>
+      </c>
+      <c r="N61" s="29" t="s">
+        <v>184</v>
+      </c>
+      <c r="O61" s="24">
+        <v>0.1</v>
+      </c>
+      <c r="P61" s="30" t="s">
+        <v>185</v>
+      </c>
+      <c r="Q61" s="22">
+        <v>100</v>
+      </c>
+      <c r="R61" s="22">
+        <v>175</v>
+      </c>
+      <c r="S61" s="4">
+        <f t="shared" ref="S61:S65" si="21">S60+10000</f>
+        <v>104000</v>
+      </c>
+      <c r="T61" s="4">
+        <f>T60+10000</f>
+        <v>104000</v>
+      </c>
+      <c r="U61" s="4">
+        <f t="shared" si="17"/>
+        <v>64000</v>
+      </c>
+      <c r="V61" s="4">
+        <f>V60+2000</f>
+        <v>64000</v>
+      </c>
+      <c r="W61" s="4">
+        <f t="shared" si="20"/>
+        <v>665</v>
+      </c>
+      <c r="X61" s="4">
+        <f t="shared" si="19"/>
+        <v>505</v>
+      </c>
+      <c r="Y61" s="4">
+        <v>99.4</v>
+      </c>
+      <c r="Z61" s="4">
+        <v>99.99999</v>
+      </c>
+      <c r="AA61" s="23">
+        <v>7.4e+17</v>
+      </c>
+      <c r="AB61" s="23">
+        <v>7.4e+17</v>
+      </c>
+    </row>
+    <row r="62" customHeight="1" spans="3:28">
+      <c r="C62" s="1">
+        <v>57</v>
+      </c>
+      <c r="D62" s="1">
+        <f t="shared" si="0"/>
+        <v>5601</v>
+      </c>
+      <c r="E62" s="1">
+        <f t="shared" si="1"/>
+        <v>5700</v>
+      </c>
+      <c r="F62" s="26" t="s">
+        <v>216</v>
+      </c>
+      <c r="G62" s="14">
+        <v>100</v>
+      </c>
+      <c r="H62" s="26" t="s">
+        <v>239</v>
+      </c>
+      <c r="I62" s="14">
+        <v>0</v>
+      </c>
+      <c r="J62" s="26" t="s">
+        <v>241</v>
+      </c>
+      <c r="K62" s="14">
+        <v>100</v>
+      </c>
+      <c r="L62" s="26" t="s">
+        <v>192</v>
+      </c>
+      <c r="M62" s="14">
+        <v>100</v>
+      </c>
+      <c r="N62" s="26" t="s">
+        <v>242</v>
+      </c>
+      <c r="O62" s="14">
+        <v>0.1</v>
+      </c>
+      <c r="P62" s="28" t="s">
+        <v>195</v>
+      </c>
+      <c r="Q62" s="1">
+        <v>100</v>
+      </c>
+      <c r="R62" s="1">
+        <v>175</v>
+      </c>
+      <c r="S62" s="15">
+        <f t="shared" si="21"/>
+        <v>114000</v>
+      </c>
+      <c r="T62" s="15">
+        <f t="shared" si="16"/>
+        <v>107000</v>
+      </c>
+      <c r="U62" s="15">
+        <f t="shared" si="17"/>
+        <v>66000</v>
+      </c>
+      <c r="V62" s="15">
+        <f t="shared" si="18"/>
+        <v>66000</v>
+      </c>
+      <c r="W62" s="15">
+        <f t="shared" si="20"/>
+        <v>685</v>
+      </c>
+      <c r="X62" s="15">
+        <f t="shared" si="19"/>
+        <v>520</v>
+      </c>
+      <c r="Y62" s="15">
+        <v>99.4</v>
+      </c>
+      <c r="Z62" s="15">
+        <v>99.99999</v>
+      </c>
+      <c r="AA62" s="13">
+        <v>7.6e+17</v>
+      </c>
+      <c r="AB62" s="13">
+        <v>7.6e+17</v>
+      </c>
+    </row>
+    <row r="63" customHeight="1" spans="3:28">
+      <c r="C63" s="1">
+        <v>58</v>
+      </c>
+      <c r="D63" s="1">
+        <f t="shared" si="0"/>
+        <v>5701</v>
+      </c>
+      <c r="E63" s="1">
+        <f t="shared" si="1"/>
+        <v>5800</v>
+      </c>
+      <c r="F63" s="26" t="s">
+        <v>221</v>
+      </c>
+      <c r="G63" s="14">
+        <v>100</v>
+      </c>
+      <c r="H63" s="26" t="s">
+        <v>239</v>
+      </c>
+      <c r="I63" s="14">
+        <v>0</v>
+      </c>
+      <c r="J63" s="26" t="s">
+        <v>243</v>
+      </c>
+      <c r="K63" s="14">
+        <v>100</v>
+      </c>
+      <c r="L63" s="26" t="s">
+        <v>197</v>
+      </c>
+      <c r="M63" s="14">
+        <v>100</v>
+      </c>
+      <c r="N63" s="26" t="s">
+        <v>244</v>
+      </c>
+      <c r="O63" s="14">
+        <v>0.1</v>
+      </c>
+      <c r="P63" s="28" t="s">
+        <v>245</v>
+      </c>
+      <c r="Q63" s="1">
+        <v>100</v>
+      </c>
+      <c r="R63" s="1">
+        <v>175</v>
+      </c>
+      <c r="S63" s="15">
+        <f t="shared" si="21"/>
+        <v>124000</v>
+      </c>
+      <c r="T63" s="15">
+        <f t="shared" si="16"/>
+        <v>110000</v>
+      </c>
+      <c r="U63" s="15">
+        <f t="shared" si="17"/>
+        <v>68000</v>
+      </c>
+      <c r="V63" s="15">
+        <f t="shared" si="18"/>
+        <v>68000</v>
+      </c>
+      <c r="W63" s="15">
+        <f t="shared" si="20"/>
+        <v>705</v>
+      </c>
+      <c r="X63" s="15">
+        <f t="shared" si="19"/>
+        <v>535</v>
+      </c>
+      <c r="Y63" s="15">
+        <v>99.4</v>
+      </c>
+      <c r="Z63" s="15">
+        <v>99.99999</v>
+      </c>
+      <c r="AA63" s="13">
+        <v>7.8e+17</v>
+      </c>
+      <c r="AB63" s="13">
+        <v>7.8e+17</v>
+      </c>
+    </row>
+    <row r="64" customHeight="1" spans="3:28">
+      <c r="C64" s="1">
+        <v>59</v>
+      </c>
+      <c r="D64" s="1">
+        <f t="shared" si="0"/>
+        <v>5801</v>
+      </c>
+      <c r="E64" s="1">
+        <f t="shared" si="1"/>
+        <v>5900</v>
+      </c>
+      <c r="F64" s="26" t="s">
+        <v>225</v>
+      </c>
+      <c r="G64" s="14">
+        <v>100</v>
+      </c>
+      <c r="H64" s="26" t="s">
+        <v>239</v>
+      </c>
+      <c r="I64" s="14">
+        <v>0</v>
+      </c>
+      <c r="J64" s="26" t="s">
+        <v>246</v>
+      </c>
+      <c r="K64" s="14">
+        <v>100</v>
+      </c>
+      <c r="L64" s="26" t="s">
+        <v>202</v>
+      </c>
+      <c r="M64" s="14">
+        <v>100</v>
+      </c>
+      <c r="N64" s="26" t="s">
+        <v>189</v>
+      </c>
+      <c r="O64" s="14">
+        <v>0.1</v>
+      </c>
+      <c r="P64" s="28" t="s">
+        <v>247</v>
+      </c>
+      <c r="Q64" s="1">
+        <v>100</v>
+      </c>
+      <c r="R64" s="1">
+        <v>175</v>
+      </c>
+      <c r="S64" s="15">
+        <f t="shared" si="21"/>
+        <v>134000</v>
+      </c>
+      <c r="T64" s="15">
+        <f t="shared" si="16"/>
+        <v>113000</v>
+      </c>
+      <c r="U64" s="15">
+        <f t="shared" si="17"/>
+        <v>70000</v>
+      </c>
+      <c r="V64" s="15">
+        <f t="shared" si="18"/>
+        <v>70000</v>
+      </c>
+      <c r="W64" s="15">
+        <f t="shared" si="20"/>
+        <v>725</v>
+      </c>
+      <c r="X64" s="15">
+        <f t="shared" si="19"/>
+        <v>550</v>
+      </c>
+      <c r="Y64" s="15">
+        <v>99.4</v>
+      </c>
+      <c r="Z64" s="15">
+        <v>99.99999</v>
+      </c>
+      <c r="AA64" s="13">
+        <v>8e+17</v>
+      </c>
+      <c r="AB64" s="13">
+        <v>8e+17</v>
+      </c>
+    </row>
+    <row r="65" customHeight="1" spans="3:28">
+      <c r="C65" s="1">
+        <v>60</v>
+      </c>
+      <c r="D65" s="1">
+        <f t="shared" si="0"/>
+        <v>5901</v>
+      </c>
+      <c r="E65" s="1">
+        <f t="shared" si="1"/>
+        <v>6000</v>
+      </c>
+      <c r="F65" s="26" t="s">
+        <v>229</v>
+      </c>
+      <c r="G65" s="14">
+        <v>100</v>
+      </c>
+      <c r="H65" s="26" t="s">
+        <v>239</v>
+      </c>
+      <c r="I65" s="14">
+        <v>0</v>
+      </c>
+      <c r="J65" s="26" t="s">
+        <v>248</v>
+      </c>
+      <c r="K65" s="14">
+        <v>100</v>
+      </c>
+      <c r="L65" s="26" t="s">
+        <v>207</v>
+      </c>
+      <c r="M65" s="14">
+        <v>100</v>
+      </c>
+      <c r="N65" s="26" t="s">
+        <v>249</v>
+      </c>
+      <c r="O65" s="14">
+        <v>0.1</v>
+      </c>
+      <c r="P65" s="28" t="s">
+        <v>250</v>
+      </c>
+      <c r="Q65" s="1">
+        <v>100</v>
+      </c>
+      <c r="R65" s="1">
+        <v>175</v>
+      </c>
+      <c r="S65" s="15">
+        <f t="shared" si="21"/>
+        <v>144000</v>
+      </c>
+      <c r="T65" s="15">
+        <f t="shared" si="16"/>
+        <v>116000</v>
+      </c>
+      <c r="U65" s="15">
+        <f t="shared" si="17"/>
+        <v>72000</v>
+      </c>
+      <c r="V65" s="15">
+        <f t="shared" si="18"/>
+        <v>72000</v>
+      </c>
+      <c r="W65" s="15">
+        <f t="shared" si="20"/>
+        <v>745</v>
+      </c>
+      <c r="X65" s="15">
+        <f t="shared" si="19"/>
+        <v>565</v>
+      </c>
+      <c r="Y65" s="15">
+        <v>99.4</v>
+      </c>
+      <c r="Z65" s="15">
+        <v>99.99999</v>
+      </c>
+      <c r="AA65" s="13">
+        <v>8.2e+17</v>
+      </c>
+      <c r="AB65" s="13">
+        <v>8.2e+17</v>
+      </c>
+    </row>
+    <row r="66" customHeight="1" spans="3:28">
+      <c r="P66" s="1"/>
+      <c r="Q66" s="1"/>
+      <c r="R66" s="1"/>
+    </row>
+    <row r="67" customHeight="1" spans="3:28">
+      <c r="P67" s="1"/>
+      <c r="Q67" s="1"/>
+      <c r="R67" s="1"/>
+    </row>
+    <row r="68" customHeight="1" spans="3:28">
+      <c r="P68" s="1"/>
+      <c r="Q68" s="1"/>
+      <c r="R68" s="1"/>
+    </row>
+    <row r="69" customHeight="1" spans="3:28">
+      <c r="P69" s="1"/>
+      <c r="Q69" s="1"/>
+      <c r="R69" s="1"/>
+    </row>
+    <row r="70" customHeight="1" spans="3:28">
+      <c r="P70" s="1"/>
+      <c r="Q70" s="1"/>
+      <c r="R70" s="1"/>
+    </row>
+    <row r="71" customHeight="1" spans="3:28">
+      <c r="P71" s="1"/>
+      <c r="Q71" s="1"/>
+      <c r="R71" s="1"/>
+    </row>
+    <row r="72" customHeight="1" spans="3:28">
+      <c r="P72" s="1"/>
+      <c r="Q72" s="1"/>
+      <c r="R72" s="1"/>
+    </row>
+    <row r="73" customHeight="1" spans="3:28">
+      <c r="P73" s="1"/>
+      <c r="Q73" s="1"/>
+      <c r="R73" s="1"/>
+    </row>
+    <row r="74" customHeight="1" spans="3:28">
+      <c r="P74" s="1"/>
+      <c r="Q74" s="1"/>
+      <c r="R74" s="1"/>
+    </row>
+    <row r="75" customHeight="1" spans="3:28">
+      <c r="P75" s="1"/>
+      <c r="Q75" s="1"/>
+      <c r="R75" s="1"/>
+    </row>
+    <row r="76" customHeight="1" spans="3:28">
+      <c r="P76" s="1"/>
+      <c r="Q76" s="1"/>
+      <c r="R76" s="1"/>
+    </row>
+    <row r="77" customHeight="1" spans="3:28">
+      <c r="P77" s="1"/>
+      <c r="Q77" s="1"/>
+      <c r="R77" s="1"/>
+    </row>
+    <row r="78" customHeight="1" spans="3:28">
+      <c r="P78" s="1"/>
+      <c r="Q78" s="1"/>
+      <c r="R78" s="1"/>
+    </row>
+    <row r="79" customHeight="1" spans="3:28">
+      <c r="P79" s="1"/>
+      <c r="Q79" s="1"/>
+      <c r="R79" s="1"/>
+    </row>
+    <row r="80" customHeight="1" spans="3:28">
+      <c r="P80" s="1"/>
+      <c r="Q80" s="1"/>
+      <c r="R80" s="1"/>
+    </row>
+    <row r="81" customHeight="1" spans="16:18">
+      <c r="P81" s="1"/>
+      <c r="Q81" s="1"/>
+      <c r="R81" s="1"/>
+    </row>
+    <row r="82" customHeight="1" spans="16:18">
+      <c r="P82" s="1"/>
+      <c r="Q82" s="1"/>
+      <c r="R82" s="1"/>
+    </row>
+    <row r="83" customHeight="1" spans="16:18">
+      <c r="P83" s="1"/>
+      <c r="Q83" s="1"/>
+      <c r="R83" s="1"/>
+    </row>
+    <row r="84" customHeight="1" spans="16:18">
+      <c r="P84" s="1"/>
+      <c r="Q84" s="1"/>
+      <c r="R84" s="1"/>
+    </row>
+    <row r="85" customHeight="1" spans="16:18">
+      <c r="P85" s="1"/>
+      <c r="Q85" s="1"/>
+      <c r="R85" s="1"/>
+    </row>
+    <row r="86" customHeight="1" spans="16:18">
+      <c r="P86" s="1"/>
+      <c r="Q86" s="1"/>
+      <c r="R86" s="1"/>
+    </row>
+    <row r="87" customHeight="1" spans="16:18">
+      <c r="P87" s="1"/>
+      <c r="Q87" s="1"/>
+      <c r="R87" s="1"/>
+    </row>
+    <row r="88" customHeight="1" spans="16:18">
+      <c r="P88" s="1"/>
+      <c r="Q88" s="1"/>
+      <c r="R88" s="1"/>
+    </row>
+    <row r="89" customHeight="1" spans="16:18">
+      <c r="P89" s="1"/>
+      <c r="Q89" s="1"/>
+      <c r="R89" s="1"/>
+    </row>
+    <row r="90" customHeight="1" spans="16:18">
+      <c r="P90" s="1"/>
+      <c r="Q90" s="1"/>
+      <c r="R90" s="1"/>
+    </row>
+    <row r="91" customHeight="1" spans="16:18">
+      <c r="P91" s="1"/>
+      <c r="Q91" s="1"/>
+      <c r="R91" s="1"/>
+    </row>
+    <row r="92" customHeight="1" spans="16:18">
+      <c r="P92" s="1"/>
+      <c r="Q92" s="1"/>
+      <c r="R92" s="1"/>
+    </row>
+    <row r="93" customHeight="1" spans="16:18">
+      <c r="P93" s="1"/>
+      <c r="Q93" s="1"/>
+      <c r="R93" s="1"/>
+    </row>
+    <row r="94" customHeight="1" spans="16:18">
+      <c r="P94" s="1"/>
+      <c r="Q94" s="1"/>
+      <c r="R94" s="1"/>
+    </row>
+    <row r="95" customHeight="1" spans="16:18">
+      <c r="P95" s="1"/>
+      <c r="Q95" s="1"/>
+      <c r="R95" s="1"/>
+    </row>
+    <row r="96" customHeight="1" spans="16:18">
+      <c r="P96" s="1"/>
+      <c r="Q96" s="1"/>
+      <c r="R96" s="1"/>
+    </row>
+    <row r="97" customHeight="1" spans="16:18">
+      <c r="P97" s="1"/>
+      <c r="Q97" s="1"/>
+      <c r="R97" s="1"/>
+    </row>
+    <row r="98" customHeight="1" spans="16:18">
+      <c r="P98" s="1"/>
+      <c r="Q98" s="1"/>
+      <c r="R98" s="1"/>
+    </row>
+    <row r="99" customHeight="1" spans="16:18">
+      <c r="P99" s="1"/>
+      <c r="Q99" s="1"/>
+      <c r="R99" s="1"/>
+    </row>
+    <row r="100" customHeight="1" spans="16:18">
+      <c r="P100" s="1"/>
+      <c r="Q100" s="1"/>
+      <c r="R100" s="1"/>
+    </row>
+    <row r="101" customHeight="1" spans="16:18">
+      <c r="P101" s="1"/>
+      <c r="Q101" s="1"/>
+      <c r="R101" s="1"/>
+    </row>
+    <row r="102" customHeight="1" spans="16:18">
+      <c r="P102" s="1"/>
+      <c r="Q102" s="1"/>
+      <c r="R102" s="1"/>
+    </row>
+    <row r="103" customHeight="1" spans="16:18">
+      <c r="P103" s="1"/>
+      <c r="Q103" s="1"/>
+      <c r="R103" s="1"/>
+    </row>
+    <row r="104" customHeight="1" spans="16:18">
+      <c r="P104" s="1"/>
+      <c r="Q104" s="1"/>
+      <c r="R104" s="1"/>
+    </row>
+    <row r="105" customHeight="1" spans="16:18">
+      <c r="P105" s="1"/>
+      <c r="Q105" s="1"/>
+      <c r="R105" s="1"/>
+    </row>
+    <row r="106" customHeight="1" spans="16:18">
+      <c r="P106" s="1"/>
+      <c r="Q106" s="1"/>
+      <c r="R106" s="1"/>
+    </row>
+    <row r="107" customHeight="1" spans="16:18">
+      <c r="P107" s="1"/>
+      <c r="Q107" s="1"/>
+      <c r="R107" s="1"/>
+    </row>
+    <row r="108" customHeight="1" spans="16:18">
+      <c r="P108" s="1"/>
+      <c r="Q108" s="1"/>
+      <c r="R108" s="1"/>
+    </row>
+    <row r="109" customHeight="1" spans="16:18">
+      <c r="P109" s="1"/>
+      <c r="Q109" s="1"/>
+      <c r="R109" s="1"/>
+    </row>
+    <row r="110" customHeight="1" spans="16:18">
+      <c r="P110" s="1"/>
+      <c r="Q110" s="1"/>
+      <c r="R110" s="1"/>
+    </row>
+    <row r="111" customHeight="1" spans="16:18">
+      <c r="P111" s="1"/>
+      <c r="Q111" s="1"/>
+      <c r="R111" s="1"/>
+    </row>
+    <row r="112" customHeight="1" spans="16:18">
+      <c r="P112" s="1"/>
+      <c r="Q112" s="1"/>
+      <c r="R112" s="1"/>
+    </row>
+    <row r="113" customHeight="1" spans="16:18">
+      <c r="P113" s="1"/>
+      <c r="Q113" s="1"/>
+      <c r="R113" s="1"/>
+    </row>
+    <row r="114" customHeight="1" spans="16:18">
+      <c r="P114" s="1"/>
+      <c r="Q114" s="1"/>
+      <c r="R114" s="1"/>
+    </row>
+    <row r="115" customHeight="1" spans="16:18">
+      <c r="P115" s="1"/>
+      <c r="Q115" s="1"/>
+      <c r="R115" s="1"/>
+    </row>
+    <row r="116" customHeight="1" spans="16:18">
+      <c r="P116" s="1"/>
+      <c r="Q116" s="1"/>
+      <c r="R116" s="1"/>
+    </row>
+    <row r="117" customHeight="1" spans="16:18">
+      <c r="P117" s="1"/>
+      <c r="Q117" s="1"/>
+      <c r="R117" s="1"/>
+    </row>
+    <row r="118" customHeight="1" spans="16:18">
+      <c r="P118" s="1"/>
+      <c r="Q118" s="1"/>
+      <c r="R118" s="1"/>
+    </row>
+    <row r="119" customHeight="1" spans="16:18">
+      <c r="P119" s="1"/>
+      <c r="Q119" s="1"/>
+      <c r="R119" s="1"/>
+    </row>
+    <row r="120" customHeight="1" spans="16:18">
+      <c r="P120" s="1"/>
+      <c r="Q120" s="1"/>
+      <c r="R120" s="1"/>
+    </row>
+    <row r="121" customHeight="1" spans="16:18">
+      <c r="P121" s="1"/>
+      <c r="Q121" s="1"/>
+      <c r="R121" s="1"/>
+    </row>
+    <row r="122" customHeight="1" spans="16:18">
+      <c r="P122" s="1"/>
+      <c r="Q122" s="1"/>
+      <c r="R122" s="1"/>
+    </row>
+    <row r="123" customHeight="1" spans="16:18">
+      <c r="P123" s="1"/>
+      <c r="Q123" s="1"/>
+      <c r="R123" s="1"/>
+    </row>
+    <row r="124" customHeight="1" spans="16:18">
+      <c r="P124" s="1"/>
+      <c r="Q124" s="1"/>
+      <c r="R124" s="1"/>
+    </row>
+    <row r="125" customHeight="1" spans="16:18">
+      <c r="P125" s="1"/>
+      <c r="Q125" s="1"/>
+      <c r="R125" s="1"/>
+    </row>
+    <row r="126" customHeight="1" spans="16:18">
+      <c r="P126" s="1"/>
+      <c r="Q126" s="1"/>
+      <c r="R126" s="1"/>
+    </row>
+    <row r="127" customHeight="1" spans="16:18">
+      <c r="P127" s="1"/>
+      <c r="Q127" s="1"/>
+      <c r="R127" s="1"/>
+    </row>
+    <row r="128" customHeight="1" spans="16:18">
+      <c r="P128" s="1"/>
+      <c r="Q128" s="1"/>
+      <c r="R128" s="1"/>
+    </row>
+    <row r="129" customHeight="1" spans="16:18">
+      <c r="P129" s="1"/>
+      <c r="Q129" s="1"/>
+      <c r="R129" s="1"/>
+    </row>
+    <row r="130" customHeight="1" spans="16:18">
+      <c r="P130" s="1"/>
+      <c r="Q130" s="1"/>
+      <c r="R130" s="1"/>
+    </row>
+    <row r="131" customHeight="1" spans="16:18">
+      <c r="P131" s="1"/>
+      <c r="Q131" s="1"/>
+      <c r="R131" s="1"/>
+    </row>
+    <row r="132" customHeight="1" spans="16:18">
+      <c r="P132" s="1"/>
+      <c r="Q132" s="1"/>
+      <c r="R132" s="1"/>
+    </row>
+    <row r="133" customHeight="1" spans="16:18">
+      <c r="P133" s="1"/>
+      <c r="Q133" s="1"/>
+      <c r="R133" s="1"/>
+    </row>
+    <row r="134" customHeight="1" spans="16:18">
+      <c r="P134" s="1"/>
+      <c r="Q134" s="1"/>
+      <c r="R134" s="1"/>
+    </row>
+    <row r="135" customHeight="1" spans="16:18">
+      <c r="P135" s="1"/>
+      <c r="Q135" s="1"/>
+      <c r="R135" s="1"/>
+    </row>
+    <row r="136" customHeight="1" spans="16:18">
+      <c r="P136" s="1"/>
+      <c r="Q136" s="1"/>
+      <c r="R136" s="1"/>
+    </row>
+    <row r="137" customHeight="1" spans="16:18">
+      <c r="P137" s="1"/>
+      <c r="Q137" s="1"/>
+      <c r="R137" s="1"/>
+    </row>
+    <row r="138" customHeight="1" spans="16:18">
+      <c r="P138" s="1"/>
+      <c r="Q138" s="1"/>
+      <c r="R138" s="1"/>
+    </row>
+    <row r="139" customHeight="1" spans="16:18">
+      <c r="P139" s="1"/>
+      <c r="Q139" s="1"/>
+      <c r="R139" s="1"/>
+    </row>
+    <row r="140" customHeight="1" spans="16:18">
+      <c r="P140" s="1"/>
+      <c r="Q140" s="1"/>
+      <c r="R140" s="1"/>
+    </row>
+    <row r="141" customHeight="1" spans="16:18">
+      <c r="P141" s="1"/>
+      <c r="Q141" s="1"/>
+      <c r="R141" s="1"/>
+    </row>
+    <row r="142" customHeight="1" spans="16:18">
+      <c r="P142" s="1"/>
+      <c r="Q142" s="1"/>
+      <c r="R142" s="1"/>
+    </row>
+    <row r="143" customHeight="1" spans="16:18">
+      <c r="P143" s="1"/>
+      <c r="Q143" s="1"/>
+      <c r="R143" s="1"/>
+    </row>
+    <row r="144" customHeight="1" spans="16:18">
+      <c r="P144" s="1"/>
+      <c r="Q144" s="1"/>
+      <c r="R144" s="1"/>
+    </row>
+    <row r="145" customHeight="1" spans="16:18">
+      <c r="P145" s="1"/>
+      <c r="Q145" s="1"/>
+      <c r="R145" s="1"/>
+    </row>
+    <row r="146" customHeight="1" spans="16:18">
+      <c r="P146" s="1"/>
+      <c r="Q146" s="1"/>
+      <c r="R146" s="1"/>
+    </row>
+    <row r="147" customHeight="1" spans="16:18">
+      <c r="P147" s="1"/>
+      <c r="Q147" s="1"/>
+      <c r="R147" s="1"/>
+    </row>
+    <row r="148" customHeight="1" spans="16:18">
+      <c r="P148" s="1"/>
+      <c r="Q148" s="1"/>
+      <c r="R148" s="1"/>
+    </row>
+    <row r="149" customHeight="1" spans="16:18">
+      <c r="P149" s="1"/>
+      <c r="Q149" s="1"/>
+      <c r="R149" s="1"/>
+    </row>
+    <row r="150" customHeight="1" spans="16:18">
+      <c r="P150" s="1"/>
+      <c r="Q150" s="1"/>
+      <c r="R150" s="1"/>
+    </row>
+    <row r="151" customHeight="1" spans="16:18">
+      <c r="P151" s="1"/>
+      <c r="Q151" s="1"/>
+      <c r="R151" s="1"/>
+    </row>
+    <row r="152" customHeight="1" spans="16:18">
+      <c r="P152" s="1"/>
+      <c r="Q152" s="1"/>
+      <c r="R152" s="1"/>
+    </row>
+    <row r="153" customHeight="1" spans="16:18">
+      <c r="P153" s="1"/>
+      <c r="Q153" s="1"/>
+      <c r="R153" s="1"/>
+    </row>
+    <row r="154" customHeight="1" spans="16:18">
+      <c r="P154" s="1"/>
+      <c r="Q154" s="1"/>
+      <c r="R154" s="1"/>
+    </row>
+    <row r="155" customHeight="1" spans="16:18">
+      <c r="P155" s="1"/>
+      <c r="Q155" s="1"/>
+      <c r="R155" s="1"/>
+    </row>
+    <row r="156" customHeight="1" spans="16:18">
+      <c r="P156" s="1"/>
+      <c r="Q156" s="1"/>
+      <c r="R156" s="1"/>
+    </row>
+    <row r="157" customHeight="1" spans="16:18">
+      <c r="P157" s="1"/>
+      <c r="Q157" s="1"/>
+      <c r="R157" s="1"/>
+    </row>
+    <row r="158" customHeight="1" spans="16:18">
+      <c r="P158" s="1"/>
+      <c r="Q158" s="1"/>
+      <c r="R158" s="1"/>
+    </row>
+    <row r="159" customHeight="1" spans="16:18">
+      <c r="P159" s="1"/>
+      <c r="Q159" s="1"/>
+      <c r="R159" s="1"/>
+    </row>
+    <row r="160" customHeight="1" spans="16:18">
+      <c r="P160" s="1"/>
+      <c r="Q160" s="1"/>
+      <c r="R160" s="1"/>
+    </row>
+    <row r="161" customHeight="1" spans="16:18">
+      <c r="P161" s="1"/>
+      <c r="Q161" s="1"/>
+      <c r="R161" s="1"/>
+    </row>
+    <row r="162" customHeight="1" spans="16:18">
+      <c r="P162" s="1"/>
+      <c r="Q162" s="1"/>
+      <c r="R162" s="1"/>
+    </row>
+    <row r="163" customHeight="1" spans="16:18">
+      <c r="P163" s="1"/>
+      <c r="Q163" s="1"/>
+      <c r="R163" s="1"/>
+    </row>
+    <row r="164" customHeight="1" spans="16:18">
+      <c r="P164" s="1"/>
+      <c r="Q164" s="1"/>
+      <c r="R164" s="1"/>
+    </row>
+    <row r="165" customHeight="1" spans="16:18">
+      <c r="P165" s="1"/>
+      <c r="Q165" s="1"/>
+      <c r="R165" s="1"/>
+    </row>
+    <row r="166" customHeight="1" spans="16:18">
+      <c r="P166" s="1"/>
+      <c r="Q166" s="1"/>
+      <c r="R166" s="1"/>
+    </row>
+    <row r="167" customHeight="1" spans="16:18">
+      <c r="P167" s="1"/>
+      <c r="Q167" s="1"/>
+      <c r="R167" s="1"/>
+    </row>
+    <row r="168" customHeight="1" spans="16:18">
+      <c r="P168" s="1"/>
+      <c r="Q168" s="1"/>
+      <c r="R168" s="1"/>
+    </row>
+    <row r="169" customHeight="1" spans="16:18">
+      <c r="P169" s="1"/>
+      <c r="Q169" s="1"/>
+      <c r="R169" s="1"/>
+    </row>
+    <row r="170" customHeight="1" spans="16:18">
+      <c r="P170" s="1"/>
+      <c r="Q170" s="1"/>
+      <c r="R170" s="1"/>
+    </row>
+    <row r="171" customHeight="1" spans="16:18">
+      <c r="P171" s="1"/>
+      <c r="Q171" s="1"/>
+      <c r="R171" s="1"/>
+    </row>
+    <row r="172" customHeight="1" spans="16:18">
+      <c r="P172" s="1"/>
+      <c r="Q172" s="1"/>
+      <c r="R172" s="1"/>
+    </row>
+    <row r="173" customHeight="1" spans="16:18">
+      <c r="P173" s="1"/>
+      <c r="Q173" s="1"/>
+      <c r="R173" s="1"/>
+    </row>
+    <row r="174" customHeight="1" spans="16:18">
+      <c r="P174" s="1"/>
+      <c r="Q174" s="1"/>
+      <c r="R174" s="1"/>
+    </row>
+    <row r="175" customHeight="1" spans="16:18">
+      <c r="P175" s="1"/>
+      <c r="Q175" s="1"/>
+      <c r="R175" s="1"/>
+    </row>
+    <row r="176" customHeight="1" spans="16:18">
+      <c r="P176" s="1"/>
+      <c r="Q176" s="1"/>
+      <c r="R176" s="1"/>
+    </row>
+    <row r="177" customHeight="1" spans="16:18">
+      <c r="P177" s="1"/>
+      <c r="Q177" s="1"/>
+      <c r="R177" s="1"/>
+    </row>
+    <row r="178" customHeight="1" spans="16:18">
+      <c r="P178" s="1"/>
+      <c r="Q178" s="1"/>
+      <c r="R178" s="1"/>
+    </row>
+    <row r="179" customHeight="1" spans="16:18">
+      <c r="P179" s="1"/>
+      <c r="Q179" s="1"/>
+      <c r="R179" s="1"/>
+    </row>
+    <row r="180" customHeight="1" spans="16:18">
+      <c r="P180" s="1"/>
+      <c r="Q180" s="1"/>
+      <c r="R180" s="1"/>
+    </row>
+    <row r="181" customHeight="1" spans="16:18">
+      <c r="P181" s="31" t="s">
+        <v>251</v>
+      </c>
+      <c r="Q181" s="19"/>
+      <c r="R181" s="19"/>
+    </row>
+    <row r="182" customHeight="1" spans="16:18">
+      <c r="P182" s="32" t="s">
+        <v>252</v>
+      </c>
+      <c r="Q182" s="12"/>
+      <c r="R182" s="12"/>
+    </row>
+    <row r="183" customHeight="1" spans="16:18">
+      <c r="P183" s="32" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q183" s="12"/>
+      <c r="R183" s="12"/>
+    </row>
+    <row r="184" customHeight="1" spans="16:18">
+      <c r="P184" s="32" t="s">
+        <v>214</v>
+      </c>
+      <c r="Q184" s="12"/>
+      <c r="R184" s="12"/>
+    </row>
+    <row r="185" customHeight="1" spans="16:18">
+      <c r="P185" s="32" t="s">
+        <v>220</v>
+      </c>
+      <c r="Q185" s="12"/>
+      <c r="R185" s="12"/>
+    </row>
+    <row r="186" customHeight="1" spans="16:18">
+      <c r="P186" s="25"/>
+      <c r="Q186" s="25"/>
+      <c r="R186" s="25"/>
+    </row>
+    <row r="187" customHeight="1" spans="16:18">
+      <c r="P187" s="25"/>
+      <c r="Q187" s="25"/>
+      <c r="R187" s="25"/>
+    </row>
+    <row r="188" customHeight="1" spans="16:18">
+      <c r="P188" s="25"/>
+      <c r="Q188" s="25"/>
+      <c r="R188" s="25"/>
+    </row>
+    <row r="189" customHeight="1" spans="16:18">
+      <c r="P189" s="25"/>
+      <c r="Q189" s="25"/>
+      <c r="R189" s="25"/>
+    </row>
+    <row r="190" customHeight="1" spans="16:18">
+      <c r="P190" s="25"/>
+      <c r="Q190" s="25"/>
+      <c r="R190" s="25"/>
+    </row>
+    <row r="191" customHeight="1" spans="16:18">
+      <c r="P191" s="25"/>
+      <c r="Q191" s="25"/>
+      <c r="R191" s="25"/>
+    </row>
+    <row r="192" customHeight="1" spans="16:18">
+      <c r="P192" s="25"/>
+      <c r="Q192" s="25"/>
+      <c r="R192" s="25"/>
+    </row>
+    <row r="193" customHeight="1" spans="16:18">
+      <c r="P193" s="25"/>
+      <c r="Q193" s="25"/>
+      <c r="R193" s="25"/>
+    </row>
+    <row r="194" customHeight="1" spans="16:18">
+      <c r="P194" s="25"/>
+      <c r="Q194" s="25"/>
+      <c r="R194" s="25"/>
+    </row>
+    <row r="195" customHeight="1" spans="16:18">
+      <c r="P195" s="25"/>
+      <c r="Q195" s="25"/>
+      <c r="R195" s="25"/>
+    </row>
+    <row r="196" customHeight="1" spans="16:18">
+      <c r="P196" s="25"/>
+      <c r="Q196" s="25"/>
+      <c r="R196" s="25"/>
+    </row>
+    <row r="197" customHeight="1" spans="16:18">
+      <c r="P197" s="25"/>
+      <c r="Q197" s="25"/>
+      <c r="R197" s="25"/>
+    </row>
+    <row r="198" customHeight="1" spans="16:18">
+      <c r="P198" s="25"/>
+      <c r="Q198" s="25"/>
+      <c r="R198" s="25"/>
+    </row>
+    <row r="199" customHeight="1" spans="16:18">
+      <c r="P199" s="25"/>
+      <c r="Q199" s="25"/>
+      <c r="R199" s="25"/>
+    </row>
+    <row r="200" customHeight="1" spans="16:18">
+      <c r="P200" s="25"/>
+      <c r="Q200" s="25"/>
+      <c r="R200" s="25"/>
+    </row>
+    <row r="201" customHeight="1" spans="16:18">
+      <c r="P201" s="25"/>
+      <c r="Q201" s="25"/>
+      <c r="R201" s="25"/>
+    </row>
+    <row r="202" customHeight="1" spans="16:18">
+      <c r="P202" s="25"/>
+      <c r="Q202" s="25"/>
+      <c r="R202" s="25"/>
+    </row>
+    <row r="203" customHeight="1" spans="16:18">
+      <c r="P203" s="25"/>
+      <c r="Q203" s="25"/>
+      <c r="R203" s="25"/>
+    </row>
+    <row r="204" customHeight="1" spans="16:18">
+      <c r="P204" s="25"/>
+      <c r="Q204" s="25"/>
+      <c r="R204" s="25"/>
+    </row>
+    <row r="205" customHeight="1" spans="16:18">
+      <c r="P205" s="25"/>
+      <c r="Q205" s="25"/>
+      <c r="R205" s="25"/>
+    </row>
+    <row r="206" customHeight="1" spans="16:18">
+      <c r="P206" s="25"/>
+      <c r="Q206" s="25"/>
+      <c r="R206" s="25"/>
+    </row>
+    <row r="207" customHeight="1" spans="16:18">
+      <c r="P207" s="25"/>
+      <c r="Q207" s="25"/>
+      <c r="R207" s="25"/>
+    </row>
+    <row r="208" customHeight="1" spans="16:18">
+      <c r="P208" s="25"/>
+      <c r="Q208" s="25"/>
+      <c r="R208" s="25"/>
+    </row>
+    <row r="209" customHeight="1" spans="16:18">
+      <c r="P209" s="25"/>
+      <c r="Q209" s="25"/>
+      <c r="R209" s="25"/>
+    </row>
+    <row r="210" customHeight="1" spans="16:18">
+      <c r="P210" s="25"/>
+      <c r="Q210" s="25"/>
+      <c r="R210" s="25"/>
+    </row>
+    <row r="211" customHeight="1" spans="16:18">
+      <c r="P211" s="25"/>
+      <c r="Q211" s="25"/>
+      <c r="R211" s="25"/>
+    </row>
+    <row r="212" customHeight="1" spans="16:18">
+      <c r="P212" s="25"/>
+      <c r="Q212" s="25"/>
+      <c r="R212" s="25"/>
+    </row>
+    <row r="213" customHeight="1" spans="16:18">
+      <c r="P213" s="25"/>
+      <c r="Q213" s="25"/>
+      <c r="R213" s="25"/>
+    </row>
+    <row r="214" customHeight="1" spans="16:18">
+      <c r="P214" s="25"/>
+      <c r="Q214" s="25"/>
+      <c r="R214" s="25"/>
+    </row>
+    <row r="215" customHeight="1" spans="16:18">
+      <c r="P215" s="25"/>
+      <c r="Q215" s="25"/>
+      <c r="R215" s="25"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="D3 E3 F3 G3 H3 I3 J3 K3 D4 E4 F4 G4 H4 I4 J4 K4 C5 D5 E5 F5 G5 H5 I5 J5 K5 L5 M5 N5 O5 P5 Q5 C3:C4 L3:L4 M3:M4 N3:N4 O3:O4 P3:P4 Q3:Q4" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:Z5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/InfiniteConfig.xlsx
+++ b/Excel/InfiniteConfig.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="35">
   <si>
     <t>#</t>
   </si>
@@ -115,25 +115,31 @@
     <t>1E+5</t>
   </si>
   <si>
-    <t>1.116</t>
-  </si>
-  <si>
-    <t>1E+4</t>
-  </si>
-  <si>
-    <t>1.0116</t>
-  </si>
-  <si>
-    <t>10E+7</t>
-  </si>
-  <si>
-    <t>1.0151</t>
-  </si>
-  <si>
-    <t>4E+7</t>
-  </si>
-  <si>
-    <t>8E+6</t>
+    <t>1.0471</t>
+  </si>
+  <si>
+    <t>5E+5</t>
+  </si>
+  <si>
+    <t>1E+7</t>
+  </si>
+  <si>
+    <t>1.0544</t>
+  </si>
+  <si>
+    <t>5E+7</t>
+  </si>
+  <si>
+    <t>2E+9</t>
+  </si>
+  <si>
+    <t>1E+9</t>
+  </si>
+  <si>
+    <t>5E+9</t>
+  </si>
+  <si>
+    <t>4E+11</t>
   </si>
 </sst>
 </file>
@@ -1127,7 +1133,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:W165"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="24" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.83333333333333" style="2" customWidth="1"/>
     <col min="2" max="2" width="6.25" style="2" customWidth="1"/>
@@ -1413,16 +1419,16 @@
         <v>27</v>
       </c>
       <c r="I6" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="J6" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="J6" s="13" t="s">
+      <c r="K6" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="K6" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="L6" s="1">
-        <v>0</v>
+      <c r="L6" s="9">
+        <v>10</v>
       </c>
       <c r="M6" s="9">
         <v>30</v>
@@ -1450,12 +1456,12 @@
         <v>10</v>
       </c>
       <c r="U6" s="10">
-        <f t="shared" ref="U6:U15" si="1">W6*10000</f>
-        <v>10000</v>
+        <f t="shared" ref="U6:U15" si="1">W6*50000</f>
+        <v>50000</v>
       </c>
       <c r="V6" s="10">
-        <f t="shared" ref="V6:V15" si="2">W6*10000</f>
-        <v>10000</v>
+        <f t="shared" ref="V6:V15" si="2">W6*50000</f>
+        <v>50000</v>
       </c>
       <c r="W6" s="2">
         <v>1</v>
@@ -1474,25 +1480,26 @@
         <v>200</v>
       </c>
       <c r="F7" s="13" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="G7" s="13" t="s">
         <v>26</v>
       </c>
       <c r="H7" s="13" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I7" s="13" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J7" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="K7" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="K7" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="L7" s="1">
-        <v>0</v>
+      <c r="L7" s="9">
+        <f>L6+10</f>
+        <v>20</v>
       </c>
       <c r="M7" s="9">
         <f t="shared" ref="M7:M15" si="5">M6+30</f>
@@ -1526,23 +1533,17 @@
       </c>
       <c r="U7" s="10">
         <f t="shared" si="1"/>
-        <v>20000</v>
+        <v>100000</v>
       </c>
       <c r="V7" s="10">
         <f t="shared" si="2"/>
-        <v>20000</v>
+        <v>100000</v>
       </c>
       <c r="W7" s="2">
         <v>2</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="1:23">
-      <c r="A8" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>0</v>
-      </c>
       <c r="C8" s="1">
         <v>3</v>
       </c>
@@ -1554,14 +1555,27 @@
         <f t="shared" si="4"/>
         <v>300</v>
       </c>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7"/>
-      <c r="H8" s="7"/>
-      <c r="I8" s="7"/>
-      <c r="J8" s="7"/>
-      <c r="K8" s="7"/>
-      <c r="L8" s="1">
-        <v>0</v>
+      <c r="F8" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="G8" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="H8" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="I8" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="J8" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="K8" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="L8" s="9">
+        <f>L7+10</f>
+        <v>30</v>
       </c>
       <c r="M8" s="9">
         <f t="shared" si="5"/>
@@ -1595,11 +1609,11 @@
       </c>
       <c r="U8" s="10">
         <f t="shared" si="1"/>
-        <v>30000</v>
+        <v>150000</v>
       </c>
       <c r="V8" s="10">
         <f t="shared" si="2"/>
-        <v>30000</v>
+        <v>150000</v>
       </c>
       <c r="W8" s="2">
         <v>3</v>
@@ -1664,11 +1678,11 @@
       </c>
       <c r="U9" s="10">
         <f t="shared" si="1"/>
-        <v>40000</v>
+        <v>200000</v>
       </c>
       <c r="V9" s="10">
         <f t="shared" si="2"/>
-        <v>40000</v>
+        <v>200000</v>
       </c>
       <c r="W9" s="2">
         <v>4</v>
@@ -1733,11 +1747,11 @@
       </c>
       <c r="U10" s="10">
         <f t="shared" si="1"/>
-        <v>50000</v>
+        <v>250000</v>
       </c>
       <c r="V10" s="10">
         <f t="shared" si="2"/>
-        <v>50000</v>
+        <v>250000</v>
       </c>
       <c r="W10" s="2">
         <v>5</v>
@@ -1802,11 +1816,11 @@
       </c>
       <c r="U11" s="10">
         <f t="shared" si="1"/>
-        <v>60000</v>
+        <v>300000</v>
       </c>
       <c r="V11" s="10">
         <f t="shared" si="2"/>
-        <v>60000</v>
+        <v>300000</v>
       </c>
       <c r="W11" s="2">
         <v>6</v>
@@ -1871,11 +1885,11 @@
       </c>
       <c r="U12" s="10">
         <f t="shared" si="1"/>
-        <v>70000</v>
+        <v>350000</v>
       </c>
       <c r="V12" s="10">
         <f t="shared" si="2"/>
-        <v>70000</v>
+        <v>350000</v>
       </c>
       <c r="W12" s="2">
         <v>7</v>
@@ -1940,11 +1954,11 @@
       </c>
       <c r="U13" s="10">
         <f t="shared" si="1"/>
-        <v>80000</v>
+        <v>400000</v>
       </c>
       <c r="V13" s="10">
         <f t="shared" si="2"/>
-        <v>80000</v>
+        <v>400000</v>
       </c>
       <c r="W13" s="2">
         <v>8</v>
@@ -2003,11 +2017,11 @@
       </c>
       <c r="U14" s="10">
         <f t="shared" si="1"/>
-        <v>90000</v>
+        <v>450000</v>
       </c>
       <c r="V14" s="10">
         <f t="shared" si="2"/>
-        <v>90000</v>
+        <v>450000</v>
       </c>
       <c r="W14" s="2">
         <v>9</v>
@@ -2066,11 +2080,11 @@
       </c>
       <c r="U15" s="10">
         <f t="shared" si="1"/>
-        <v>100000</v>
+        <v>500000</v>
       </c>
       <c r="V15" s="10">
         <f t="shared" si="2"/>
-        <v>100000</v>
+        <v>500000</v>
       </c>
       <c r="W15" s="2">
         <v>10</v>
@@ -2528,7 +2542,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="S5:T5 S3:S4 T3:T4 C3:K5 L3:R5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:T5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/InfiniteConfig.xlsx
+++ b/Excel/InfiniteConfig.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="35">
   <si>
     <t>#</t>
   </si>
@@ -115,31 +115,31 @@
     <t>1E+5</t>
   </si>
   <si>
-    <t>1.0471</t>
-  </si>
-  <si>
     <t>5E+5</t>
   </si>
   <si>
     <t>1E+7</t>
   </si>
   <si>
-    <t>1.0544</t>
-  </si>
-  <si>
-    <t>5E+7</t>
-  </si>
-  <si>
-    <t>2E+9</t>
-  </si>
-  <si>
-    <t>1E+9</t>
-  </si>
-  <si>
-    <t>5E+9</t>
-  </si>
-  <si>
-    <t>4E+11</t>
+    <t>1.0423</t>
+  </si>
+  <si>
+    <t>1E+8</t>
+  </si>
+  <si>
+    <t>5E+8</t>
+  </si>
+  <si>
+    <t>4E+10</t>
+  </si>
+  <si>
+    <t>1E+11</t>
+  </si>
+  <si>
+    <t>5E+11</t>
+  </si>
+  <si>
+    <t>16E+13</t>
   </si>
 </sst>
 </file>
@@ -1407,25 +1407,25 @@
         <v>1</v>
       </c>
       <c r="E6" s="6">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F6" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="G6" s="13" t="s">
+      <c r="G6" s="7">
+        <v>1.0351</v>
+      </c>
+      <c r="H6" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="H6" s="13" t="s">
+      <c r="I6" s="7">
+        <v>1.0351</v>
+      </c>
+      <c r="J6" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="I6" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="J6" s="13" t="s">
+      <c r="K6" s="14" t="s">
         <v>28</v>
-      </c>
-      <c r="K6" s="14" t="s">
-        <v>29</v>
       </c>
       <c r="L6" s="9">
         <v>10</v>
@@ -1473,29 +1473,29 @@
       </c>
       <c r="D7" s="1">
         <f t="shared" ref="D7:D65" si="3">E6+1</f>
-        <v>101</v>
+        <v>201</v>
       </c>
       <c r="E7" s="1">
-        <f t="shared" ref="E7:E65" si="4">E6+100</f>
-        <v>200</v>
+        <f t="shared" ref="E7:E15" si="4">E6+200</f>
+        <v>400</v>
       </c>
       <c r="F7" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="G7" s="13" t="s">
-        <v>26</v>
+        <v>29</v>
+      </c>
+      <c r="G7" s="7">
+        <v>1.0351</v>
       </c>
       <c r="H7" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="I7" s="13" t="s">
-        <v>26</v>
+      <c r="I7" s="7">
+        <v>1.0351</v>
       </c>
       <c r="J7" s="13" t="s">
         <v>31</v>
       </c>
       <c r="K7" s="14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L7" s="9">
         <f>L6+10</f>
@@ -1544,34 +1544,40 @@
       </c>
     </row>
     <row r="8" customHeight="1" spans="1:23">
+      <c r="A8" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="C8" s="1">
         <v>3</v>
       </c>
       <c r="D8" s="1">
         <f t="shared" si="3"/>
-        <v>201</v>
+        <v>401</v>
       </c>
       <c r="E8" s="1">
         <f t="shared" si="4"/>
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="F8" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="G8" s="13" t="s">
-        <v>26</v>
+      <c r="G8" s="7">
+        <v>1.0351</v>
       </c>
       <c r="H8" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="I8" s="13" t="s">
-        <v>26</v>
+      <c r="I8" s="7">
+        <v>1.0351</v>
       </c>
       <c r="J8" s="13" t="s">
         <v>34</v>
       </c>
       <c r="K8" s="14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L8" s="9">
         <f>L7+10</f>
@@ -1631,11 +1637,11 @@
       </c>
       <c r="D9" s="1">
         <f t="shared" si="3"/>
-        <v>301</v>
+        <v>601</v>
       </c>
       <c r="E9" s="1">
         <f t="shared" si="4"/>
-        <v>400</v>
+        <v>800</v>
       </c>
       <c r="F9" s="7"/>
       <c r="G9" s="7"/>
@@ -1700,11 +1706,11 @@
       </c>
       <c r="D10" s="1">
         <f t="shared" si="3"/>
-        <v>401</v>
+        <v>801</v>
       </c>
       <c r="E10" s="1">
         <f t="shared" si="4"/>
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="F10" s="7"/>
       <c r="G10" s="7"/>
@@ -1769,11 +1775,11 @@
       </c>
       <c r="D11" s="1">
         <f t="shared" si="3"/>
-        <v>501</v>
+        <v>1001</v>
       </c>
       <c r="E11" s="1">
         <f t="shared" si="4"/>
-        <v>600</v>
+        <v>1200</v>
       </c>
       <c r="F11" s="7"/>
       <c r="G11" s="7"/>
@@ -1838,11 +1844,11 @@
       </c>
       <c r="D12" s="1">
         <f t="shared" si="3"/>
-        <v>601</v>
+        <v>1201</v>
       </c>
       <c r="E12" s="1">
         <f t="shared" si="4"/>
-        <v>700</v>
+        <v>1400</v>
       </c>
       <c r="F12" s="7"/>
       <c r="G12" s="7"/>
@@ -1907,11 +1913,11 @@
       </c>
       <c r="D13" s="1">
         <f t="shared" si="3"/>
-        <v>701</v>
+        <v>1401</v>
       </c>
       <c r="E13" s="1">
         <f t="shared" si="4"/>
-        <v>800</v>
+        <v>1600</v>
       </c>
       <c r="F13" s="7"/>
       <c r="G13" s="7"/>
@@ -1976,11 +1982,11 @@
       </c>
       <c r="D14" s="1">
         <f t="shared" si="3"/>
-        <v>801</v>
+        <v>1601</v>
       </c>
       <c r="E14" s="1">
         <f t="shared" si="4"/>
-        <v>900</v>
+        <v>1800</v>
       </c>
       <c r="L14" s="1">
         <v>0</v>
@@ -2039,11 +2045,11 @@
       </c>
       <c r="D15" s="1">
         <f t="shared" si="3"/>
-        <v>901</v>
+        <v>1801</v>
       </c>
       <c r="E15" s="1">
         <f t="shared" si="4"/>
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="L15" s="1">
         <v>0</v>
